--- a/research/traditional_assets/database/data/pakistan/pakistan_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_insurance_prop_cas.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0521</v>
+        <v>0.0541</v>
       </c>
       <c r="E2">
-        <v>-0.0617</v>
+        <v>0.00772</v>
       </c>
       <c r="G2">
-        <v>0.1175541842197808</v>
+        <v>0.1620248697883164</v>
       </c>
       <c r="H2">
-        <v>0.1175541842197808</v>
+        <v>0.1620248697883164</v>
       </c>
       <c r="I2">
-        <v>0.1145971437886733</v>
+        <v>0.1028183466268026</v>
       </c>
       <c r="J2">
-        <v>0.08961459684566055</v>
+        <v>0.07872003834097216</v>
       </c>
       <c r="K2">
-        <v>56.31</v>
+        <v>31.825</v>
       </c>
       <c r="L2">
-        <v>0.08216827350317597</v>
+        <v>0.05848958122746336</v>
       </c>
       <c r="M2">
-        <v>33.753</v>
+        <v>36.556</v>
       </c>
       <c r="N2">
-        <v>0.1006194626951099</v>
+        <v>0.169001322200956</v>
       </c>
       <c r="O2">
-        <v>0.599413958444326</v>
+        <v>1.14865671641791</v>
       </c>
       <c r="P2">
-        <v>33.753</v>
+        <v>29.706</v>
       </c>
       <c r="Q2">
-        <v>0.1006194626951099</v>
+        <v>0.137333222379407</v>
       </c>
       <c r="R2">
-        <v>0.599413958444326</v>
+        <v>0.9334171249018067</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>6.849999999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1873837400153189</v>
       </c>
       <c r="U2">
-        <v>157.454</v>
+        <v>117.78</v>
       </c>
       <c r="V2">
-        <v>0.4693786294313345</v>
+        <v>0.5445063937200078</v>
       </c>
       <c r="W2">
-        <v>0.08548387096774193</v>
+        <v>0.06338383838383839</v>
       </c>
       <c r="X2">
-        <v>0.1026237927880735</v>
+        <v>0.1719313508664606</v>
       </c>
       <c r="Y2">
-        <v>-0.01713992182033153</v>
+        <v>-0.1085475124826222</v>
       </c>
       <c r="Z2">
-        <v>2.28548463647951</v>
+        <v>1.806466447994428</v>
       </c>
       <c r="AA2">
-        <v>0.08670681744475575</v>
+        <v>0.09881527503056249</v>
       </c>
       <c r="AB2">
-        <v>0.1011019825706435</v>
+        <v>0.1700472069062335</v>
       </c>
       <c r="AC2">
-        <v>-0.01392027718735414</v>
+        <v>-0.07304347672675747</v>
       </c>
       <c r="AD2">
-        <v>19.011</v>
+        <v>7.037</v>
       </c>
       <c r="AE2">
-        <v>1.052313822391956</v>
+        <v>1.175490717519515</v>
       </c>
       <c r="AF2">
-        <v>20.06331382239196</v>
+        <v>8.212490717519515</v>
       </c>
       <c r="AG2">
-        <v>-137.390686177608</v>
+        <v>-109.5675092824805</v>
       </c>
       <c r="AH2">
-        <v>0.05643445737028131</v>
+        <v>0.03657823768222348</v>
       </c>
       <c r="AI2">
-        <v>0.04170184704096246</v>
+        <v>0.02262503268762527</v>
       </c>
       <c r="AJ2">
-        <v>-0.6936775462411138</v>
+        <v>-1.026504202429168</v>
       </c>
       <c r="AK2">
-        <v>-0.4244916809438742</v>
+        <v>-0.4468450094526383</v>
       </c>
       <c r="AL2">
-        <v>0.65</v>
+        <v>0.743</v>
       </c>
       <c r="AM2">
-        <v>0.646</v>
+        <v>0.743</v>
       </c>
       <c r="AN2">
-        <v>0.2201978317272053</v>
+        <v>0.1135073230531002</v>
       </c>
       <c r="AO2">
-        <v>120.4338461538461</v>
+        <v>74.92462987886945</v>
       </c>
       <c r="AP2">
-        <v>-1.591348755763622</v>
+        <v>-1.767331913066657</v>
       </c>
       <c r="AQ2">
-        <v>121.1795665634675</v>
+        <v>74.92462987886945</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adamjee Insurance Company Limited (KASE:AICL)</t>
+          <t>The United Insurance Company of Pakistan Limited (KASE:UNIC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.106</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="E3">
-        <v>0.0403</v>
+        <v>0.349</v>
       </c>
       <c r="G3">
-        <v>0.06916299559471366</v>
+        <v>0.4213836477987422</v>
       </c>
       <c r="H3">
-        <v>0.06916299559471366</v>
+        <v>0.4213836477987422</v>
       </c>
       <c r="I3">
-        <v>0.09028333049897252</v>
+        <v>0.313829747125526</v>
       </c>
       <c r="J3">
-        <v>0.07950067680904785</v>
+        <v>0.2403258348659832</v>
       </c>
       <c r="K3">
-        <v>18.6</v>
+        <v>3.76</v>
       </c>
       <c r="L3">
-        <v>0.08193832599118943</v>
+        <v>0.2364779874213836</v>
       </c>
       <c r="M3">
-        <v>5.19</v>
+        <v>3.14</v>
       </c>
       <c r="N3">
-        <v>0.06536523929471033</v>
+        <v>0.3165322580645161</v>
       </c>
       <c r="O3">
-        <v>0.2790322580645161</v>
+        <v>0.8351063829787235</v>
       </c>
       <c r="P3">
-        <v>5.19</v>
+        <v>3.14</v>
       </c>
       <c r="Q3">
-        <v>0.06536523929471033</v>
+        <v>0.3165322580645161</v>
       </c>
       <c r="R3">
-        <v>0.2790322580645161</v>
+        <v>0.8351063829787235</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>76</v>
+        <v>3.05</v>
       </c>
       <c r="V3">
-        <v>0.9571788413098236</v>
+        <v>0.3074596774193548</v>
       </c>
       <c r="W3">
-        <v>0.1463414634146342</v>
+        <v>0.1413533834586466</v>
       </c>
       <c r="X3">
-        <v>0.1082151087397481</v>
+        <v>0.1732866043811476</v>
       </c>
       <c r="Y3">
-        <v>0.03812635467488611</v>
+        <v>-0.03193322092250098</v>
       </c>
       <c r="Z3">
-        <v>3.544747050479602</v>
+        <v>0.7053958536022743</v>
       </c>
       <c r="AA3">
-        <v>0.2818097896300045</v>
+        <v>0.1695248474279695</v>
       </c>
       <c r="AB3">
-        <v>0.1022985248724542</v>
+        <v>0.1703096639379897</v>
       </c>
       <c r="AC3">
-        <v>0.1795112647575502</v>
+        <v>-0.0007848165100202142</v>
       </c>
       <c r="AD3">
-        <v>9.41</v>
+        <v>0.402</v>
       </c>
       <c r="AE3">
-        <v>0.708419883666183</v>
+        <v>0.01053510352068179</v>
       </c>
       <c r="AF3">
-        <v>10.11841988366618</v>
+        <v>0.4125351035206818</v>
       </c>
       <c r="AG3">
-        <v>-65.88158011633382</v>
+        <v>-2.637464896479318</v>
       </c>
       <c r="AH3">
-        <v>0.1130317078520331</v>
+        <v>0.03992583614645699</v>
       </c>
       <c r="AI3">
-        <v>0.07011177015257342</v>
+        <v>0.02114205567508485</v>
       </c>
       <c r="AJ3">
-        <v>-4.873467511978685</v>
+        <v>-0.3621630186450124</v>
       </c>
       <c r="AK3">
-        <v>-0.9643311456634706</v>
+        <v>-0.1602101304503988</v>
       </c>
       <c r="AL3">
-        <v>0.202</v>
+        <v>0.04</v>
       </c>
       <c r="AM3">
-        <v>0.202</v>
+        <v>0.04</v>
       </c>
       <c r="AN3">
-        <v>0.4194152255303976</v>
+        <v>0.07319737800437</v>
       </c>
       <c r="AO3">
-        <v>100.990099009901</v>
+        <v>124.5</v>
       </c>
       <c r="AP3">
-        <v>-2.936422718681308</v>
+        <v>-0.48023759950461</v>
       </c>
       <c r="AQ3">
-        <v>100.990099009901</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="4">
@@ -856,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.07769999999999999</v>
+        <v>0.0541</v>
       </c>
       <c r="E4">
-        <v>0.0584</v>
+        <v>0.00772</v>
       </c>
       <c r="G4">
-        <v>0.4842975206611571</v>
+        <v>0.7014314928425359</v>
       </c>
       <c r="H4">
-        <v>0.4842975206611571</v>
+        <v>0.7014314928425359</v>
       </c>
       <c r="I4">
-        <v>0.544877833748652</v>
+        <v>0.4871204328993705</v>
       </c>
       <c r="J4">
-        <v>0.3863065756298492</v>
+        <v>0.3115908952447999</v>
       </c>
       <c r="K4">
-        <v>4.58</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>0.3785123966942149</v>
+        <v>0.3067484662576687</v>
       </c>
       <c r="M4">
-        <v>3.41</v>
+        <v>2.57</v>
       </c>
       <c r="N4">
-        <v>0.1159863945578231</v>
+        <v>0.1122270742358079</v>
       </c>
       <c r="O4">
-        <v>0.7445414847161572</v>
+        <v>0.8566666666666666</v>
       </c>
       <c r="P4">
-        <v>3.41</v>
+        <v>2.57</v>
       </c>
       <c r="Q4">
-        <v>0.1159863945578231</v>
+        <v>0.1122270742358079</v>
       </c>
       <c r="R4">
-        <v>0.7445414847161572</v>
+        <v>0.8566666666666666</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>4.34</v>
+        <v>5.28</v>
       </c>
       <c r="V4">
-        <v>0.1476190476190476</v>
+        <v>0.2305676855895197</v>
       </c>
       <c r="W4">
-        <v>0.1892561983471074</v>
+        <v>0.1209677419354839</v>
       </c>
       <c r="X4">
-        <v>0.1015550268022745</v>
+        <v>0.1710286269109225</v>
       </c>
       <c r="Y4">
-        <v>0.08770117154483296</v>
+        <v>-0.05006088497543869</v>
       </c>
       <c r="Z4">
-        <v>0.6189292801670484</v>
+        <v>0.46801399883413</v>
       </c>
       <c r="AA4">
-        <v>0.23909645077838</v>
+        <v>0.1458289008838253</v>
       </c>
       <c r="AB4">
-        <v>0.1007657119235389</v>
+        <v>0.1699415743242982</v>
       </c>
       <c r="AC4">
-        <v>0.1383307388548412</v>
+        <v>-0.02411267344047288</v>
       </c>
       <c r="AD4">
-        <v>0.362</v>
+        <v>0.32</v>
       </c>
       <c r="AE4">
-        <v>0.1548910582065583</v>
+        <v>0.07481083122078888</v>
       </c>
       <c r="AF4">
-        <v>0.5168910582065582</v>
+        <v>0.3948108312207889</v>
       </c>
       <c r="AG4">
-        <v>-3.823108941793442</v>
+        <v>-4.885189168779211</v>
       </c>
       <c r="AH4">
-        <v>0.0172775659476411</v>
+        <v>0.01694844547488856</v>
       </c>
       <c r="AI4">
-        <v>0.02041684569476418</v>
+        <v>0.02364871547286162</v>
       </c>
       <c r="AJ4">
-        <v>-0.1494751231919865</v>
+        <v>-0.2711762679357629</v>
       </c>
       <c r="AK4">
-        <v>-0.1822533630548541</v>
+        <v>-0.4279693497344407</v>
       </c>
       <c r="AL4">
-        <v>0.06900000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="AM4">
-        <v>0.06900000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="AN4">
-        <v>0.05424033563080611</v>
+        <v>0.06531945294958155</v>
       </c>
       <c r="AO4">
-        <v>94.63768115942028</v>
+        <v>121.2820512820513</v>
       </c>
       <c r="AP4">
-        <v>-0.5728362214254482</v>
+        <v>-0.9971808876871222</v>
       </c>
       <c r="AQ4">
-        <v>94.63768115942028</v>
+        <v>121.2820512820513</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jubilee General Insurance Company Limited (KASE:JGICL)</t>
+          <t>Century Insurance Company Limited (KASE:CENI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,46 +990,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0521</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="E5">
-        <v>0.103</v>
+        <v>0.105</v>
       </c>
       <c r="G5">
-        <v>0.3004926108374384</v>
+        <v>0.4065335753176044</v>
       </c>
       <c r="H5">
-        <v>0.3004926108374384</v>
+        <v>0.4065335753176044</v>
       </c>
       <c r="I5">
-        <v>0.3103448275862069</v>
+        <v>0.3357531760435572</v>
       </c>
       <c r="J5">
-        <v>0.224037251447269</v>
+        <v>0.2146359308634468</v>
       </c>
       <c r="K5">
-        <v>9.91</v>
+        <v>1.23</v>
       </c>
       <c r="L5">
-        <v>0.2440886699507389</v>
+        <v>0.2232304900181488</v>
       </c>
       <c r="M5">
-        <v>3.95</v>
+        <v>0.493</v>
       </c>
       <c r="N5">
-        <v>0.08229166666666667</v>
+        <v>0.125765306122449</v>
       </c>
       <c r="O5">
-        <v>0.3985872855701312</v>
+        <v>0.4008130081300813</v>
       </c>
       <c r="P5">
-        <v>3.95</v>
+        <v>0.493</v>
       </c>
       <c r="Q5">
-        <v>0.08229166666666667</v>
+        <v>0.125765306122449</v>
       </c>
       <c r="R5">
-        <v>0.3985872855701312</v>
+        <v>0.4008130081300813</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1038,67 +1038,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>12.1</v>
+        <v>2.41</v>
       </c>
       <c r="V5">
-        <v>0.2520833333333333</v>
+        <v>0.614795918367347</v>
       </c>
       <c r="W5">
-        <v>0.1801818181818182</v>
+        <v>0.0984</v>
       </c>
       <c r="X5">
-        <v>0.1004891361401464</v>
+        <v>0.172103183050598</v>
       </c>
       <c r="Y5">
-        <v>0.07969268204167179</v>
+        <v>-0.07370318305059805</v>
       </c>
       <c r="Z5">
-        <v>0.9076682316118936</v>
+        <v>0.6182675044883302</v>
       </c>
       <c r="AA5">
-        <v>0.2033514958363319</v>
+        <v>0.132702421348473</v>
       </c>
       <c r="AB5">
-        <v>0.1004891361401464</v>
+        <v>0.1700472069062335</v>
       </c>
       <c r="AC5">
-        <v>0.1028623596961855</v>
+        <v>-0.03734478555776047</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>0.113</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>0.113</v>
       </c>
       <c r="AG5">
-        <v>-12.1</v>
+        <v>-2.297</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.028018844532606</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.010957044506933</v>
       </c>
       <c r="AJ5">
-        <v>-0.3370473537604457</v>
+        <v>-1.41528034504005</v>
       </c>
       <c r="AK5">
-        <v>-0.2688888888888889</v>
+        <v>-0.2906491205871189</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>0.06042780748663101</v>
+      </c>
+      <c r="AO5">
+        <v>92.5</v>
       </c>
       <c r="AP5">
-        <v>-0.9453124999999999</v>
+        <v>-1.228342245989305</v>
+      </c>
+      <c r="AQ5">
+        <v>92.5</v>
       </c>
     </row>
     <row r="6">
@@ -1118,46 +1124,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.389</v>
+        <v>0.445</v>
       </c>
       <c r="E6">
-        <v>-0.0989</v>
+        <v>-0.0717</v>
       </c>
       <c r="G6">
-        <v>0.1036886436247459</v>
+        <v>0.1288600838734273</v>
       </c>
       <c r="H6">
-        <v>0.1036886436247459</v>
+        <v>0.1288600838734273</v>
       </c>
       <c r="I6">
-        <v>0.08161487075225095</v>
+        <v>0.0770110560426992</v>
       </c>
       <c r="J6">
-        <v>0.05468471137945433</v>
+        <v>0.04199954815662021</v>
       </c>
       <c r="K6">
-        <v>14.8</v>
+        <v>7.93</v>
       </c>
       <c r="L6">
-        <v>0.04298576822538484</v>
+        <v>0.03023255813953488</v>
       </c>
       <c r="M6">
-        <v>16.4</v>
+        <v>12</v>
       </c>
       <c r="N6">
-        <v>0.1378151260504202</v>
+        <v>0.1463414634146341</v>
       </c>
       <c r="O6">
-        <v>1.108108108108108</v>
+        <v>1.513240857503153</v>
       </c>
       <c r="P6">
-        <v>16.4</v>
+        <v>12</v>
       </c>
       <c r="Q6">
-        <v>0.1378151260504202</v>
+        <v>0.1463414634146341</v>
       </c>
       <c r="R6">
-        <v>1.108108108108108</v>
+        <v>1.513240857503153</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1166,73 +1172,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>45.5</v>
+        <v>39.4</v>
       </c>
       <c r="V6">
-        <v>0.3823529411764706</v>
+        <v>0.4804878048780488</v>
       </c>
       <c r="W6">
-        <v>0.1164437450826121</v>
+        <v>0.06379726468222044</v>
       </c>
       <c r="X6">
-        <v>0.1026237927880735</v>
+        <v>0.173343080083121</v>
       </c>
       <c r="Y6">
-        <v>0.01381995229453867</v>
+        <v>-0.1095458154009006</v>
       </c>
       <c r="Z6">
-        <v>3.672533333333333</v>
+        <v>3.160621761658031</v>
       </c>
       <c r="AA6">
-        <v>0.2008314253647587</v>
+        <v>0.1327446858836183</v>
       </c>
       <c r="AB6">
-        <v>0.1010336013814763</v>
+        <v>0.1703220283530828</v>
       </c>
       <c r="AC6">
-        <v>0.09979782398328237</v>
+        <v>-0.03757734246946456</v>
       </c>
       <c r="AD6">
-        <v>4.19</v>
+        <v>3.46</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>4.19</v>
+        <v>3.46</v>
       </c>
       <c r="AG6">
-        <v>-41.31</v>
+        <v>-35.94</v>
       </c>
       <c r="AH6">
-        <v>0.03401250101469275</v>
+        <v>0.04048677743973789</v>
       </c>
       <c r="AI6">
-        <v>0.02773181547422067</v>
+        <v>0.03178394267866985</v>
       </c>
       <c r="AJ6">
-        <v>-0.5317286652078775</v>
+        <v>-0.7802865827181936</v>
       </c>
       <c r="AK6">
-        <v>-0.3912302301354295</v>
+        <v>-0.5174200978980708</v>
       </c>
       <c r="AL6">
-        <v>0.07099999999999999</v>
+        <v>0.047</v>
       </c>
       <c r="AM6">
-        <v>0.07099999999999999</v>
+        <v>0.047</v>
       </c>
       <c r="AN6">
-        <v>0.1281345565749235</v>
+        <v>0.1453781512605042</v>
       </c>
       <c r="AO6">
-        <v>395.774647887324</v>
+        <v>429.7872340425532</v>
       </c>
       <c r="AP6">
-        <v>-1.263302752293578</v>
+        <v>-1.510084033613445</v>
       </c>
       <c r="AQ6">
-        <v>395.774647887324</v>
+        <v>429.7872340425532</v>
       </c>
     </row>
     <row r="7">
@@ -1243,7 +1249,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Askari General Insurance Company Limited (KASE:AGIC)</t>
+          <t>Jubilee General Insurance Company Limited (KASE:JGICL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1252,46 +1258,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.129</v>
+        <v>0.0393</v>
       </c>
       <c r="E7">
-        <v>0.111</v>
+        <v>0.0249</v>
       </c>
       <c r="G7">
-        <v>0.2576388888888889</v>
+        <v>0.3987138263665595</v>
       </c>
       <c r="H7">
-        <v>0.2576388888888889</v>
+        <v>0.3987138263665595</v>
       </c>
       <c r="I7">
-        <v>0.225</v>
+        <v>0.280064308681672</v>
       </c>
       <c r="J7">
-        <v>0.1582075471698113</v>
+        <v>0.1764550255735302</v>
       </c>
       <c r="K7">
-        <v>2.23</v>
+        <v>6.08</v>
       </c>
       <c r="L7">
-        <v>0.1548611111111111</v>
+        <v>0.1954983922829582</v>
       </c>
       <c r="M7">
-        <v>1.15</v>
+        <v>3.38</v>
       </c>
       <c r="N7">
-        <v>0.148578811369509</v>
+        <v>0.1420168067226891</v>
       </c>
       <c r="O7">
-        <v>0.5156950672645739</v>
+        <v>0.5559210526315789</v>
       </c>
       <c r="P7">
-        <v>1.15</v>
+        <v>3.38</v>
       </c>
       <c r="Q7">
-        <v>0.148578811369509</v>
+        <v>0.1420168067226891</v>
       </c>
       <c r="R7">
-        <v>0.5156950672645739</v>
+        <v>0.5559210526315789</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1300,73 +1306,67 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.582</v>
+        <v>11.1</v>
       </c>
       <c r="V7">
-        <v>0.0751937984496124</v>
+        <v>0.4663865546218487</v>
       </c>
       <c r="W7">
-        <v>0.1784</v>
+        <v>0.1064798598949212</v>
       </c>
       <c r="X7">
-        <v>0.1104368601785921</v>
+        <v>0.1700219421079369</v>
       </c>
       <c r="Y7">
-        <v>0.06796313982140786</v>
+        <v>-0.06354208221301573</v>
       </c>
       <c r="Z7">
-        <v>1.208053691275168</v>
+        <v>0.6911111111111111</v>
       </c>
       <c r="AA7">
-        <v>0.1911232113460808</v>
+        <v>0.121950028785262</v>
       </c>
       <c r="AB7">
-        <v>0.1027455072052023</v>
+        <v>0.1695694889428743</v>
       </c>
       <c r="AC7">
-        <v>0.08837770414087848</v>
+        <v>-0.04761946015761231</v>
       </c>
       <c r="AD7">
-        <v>1.27</v>
+        <v>0.152</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1.27</v>
+        <v>0.152</v>
       </c>
       <c r="AG7">
-        <v>0.6880000000000001</v>
+        <v>-10.948</v>
       </c>
       <c r="AH7">
-        <v>0.1409544950055494</v>
+        <v>0.006346025384101536</v>
       </c>
       <c r="AI7">
-        <v>0.08837856645789841</v>
+        <v>0.003388923570855257</v>
       </c>
       <c r="AJ7">
-        <v>0.08163265306122448</v>
+        <v>-0.8518518518518519</v>
       </c>
       <c r="AK7">
-        <v>0.04989846243109951</v>
+        <v>-0.3243659634984594</v>
       </c>
       <c r="AL7">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>0.4096774193548387</v>
-      </c>
-      <c r="AO7">
-        <v>45.63380281690142</v>
+        <v>0.01729237770193402</v>
       </c>
       <c r="AP7">
-        <v>0.2219354838709678</v>
-      </c>
-      <c r="AQ7">
-        <v>45.63380281690142</v>
+        <v>-1.245506257110353</v>
       </c>
     </row>
     <row r="8">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Century Insurance Company Limited (KASE:CENI)</t>
+          <t>Askari General Insurance Company Limited (KASE:AGIC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1386,46 +1386,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.0341</v>
+        <v>0.152</v>
       </c>
       <c r="E8">
-        <v>-0.123</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="G8">
-        <v>0.3224755700325733</v>
+        <v>0.2421875</v>
       </c>
       <c r="H8">
-        <v>0.3224755700325733</v>
+        <v>0.2421875</v>
       </c>
       <c r="I8">
-        <v>0.3566775244299674</v>
+        <v>0.1939946582292999</v>
       </c>
       <c r="J8">
-        <v>0.2517291993404914</v>
+        <v>0.1297644940760695</v>
       </c>
       <c r="K8">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="L8">
-        <v>0.2785016286644951</v>
+        <v>0.12421875</v>
       </c>
       <c r="M8">
-        <v>0.587</v>
+        <v>0.87</v>
       </c>
       <c r="N8">
-        <v>0.1093109869646182</v>
+        <v>0.171259842519685</v>
       </c>
       <c r="O8">
-        <v>0.3432748538011696</v>
+        <v>0.5471698113207547</v>
       </c>
       <c r="P8">
-        <v>0.587</v>
+        <v>0.87</v>
       </c>
       <c r="Q8">
-        <v>0.1093109869646182</v>
+        <v>0.171259842519685</v>
       </c>
       <c r="R8">
-        <v>0.3432748538011696</v>
+        <v>0.5471698113207547</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1434,73 +1434,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>3.83</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0.7132216014897579</v>
+        <v>0.1988188976377953</v>
       </c>
       <c r="W8">
-        <v>0.148695652173913</v>
+        <v>0.1213740458015267</v>
       </c>
       <c r="X8">
-        <v>0.1032212704737777</v>
+        <v>0.1892632643724441</v>
       </c>
       <c r="Y8">
-        <v>0.04547438170013535</v>
+        <v>-0.06788921857091738</v>
       </c>
       <c r="Z8">
-        <v>0.6472014335406345</v>
+        <v>0.9187256612262141</v>
       </c>
       <c r="AA8">
-        <v>0.1629194986772022</v>
+        <v>0.1192179706237221</v>
       </c>
       <c r="AB8">
-        <v>0.1011794225059303</v>
+        <v>0.1747513069405028</v>
       </c>
       <c r="AC8">
-        <v>0.06174007617127192</v>
+        <v>-0.05553333631678067</v>
       </c>
       <c r="AD8">
-        <v>0.242</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>0.144341873324806</v>
       </c>
       <c r="AF8">
-        <v>0.242</v>
+        <v>1.086341873324806</v>
       </c>
       <c r="AG8">
-        <v>-3.588</v>
+        <v>0.07634187332480602</v>
       </c>
       <c r="AH8">
-        <v>0.04312188168210977</v>
+        <v>0.1761728259057855</v>
       </c>
       <c r="AI8">
-        <v>0.01899230889970177</v>
+        <v>0.0954074526665863</v>
       </c>
       <c r="AJ8">
-        <v>-2.013468013468013</v>
+        <v>0.01480543284372664</v>
       </c>
       <c r="AK8">
-        <v>-0.4026032315978457</v>
+        <v>0.007357301277925649</v>
       </c>
       <c r="AL8">
-        <v>0.034</v>
+        <v>0.097</v>
       </c>
       <c r="AM8">
-        <v>0.034</v>
+        <v>0.097</v>
       </c>
       <c r="AN8">
-        <v>0.103862660944206</v>
+        <v>0.3764988009592325</v>
       </c>
       <c r="AO8">
-        <v>64.41176470588235</v>
+        <v>25.36082474226804</v>
       </c>
       <c r="AP8">
-        <v>-1.539914163090129</v>
+        <v>0.03051233945835572</v>
       </c>
       <c r="AQ8">
-        <v>64.41176470588235</v>
+        <v>25.36082474226804</v>
       </c>
     </row>
     <row r="9">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The United Insurance Company of Pakistan Limited (KASE:UNIC)</t>
+          <t>Adamjee Insurance Company Limited (KASE:AICL)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1520,118 +1520,121 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.0244</v>
+        <v>0.0902</v>
       </c>
       <c r="E9">
-        <v>-0.0444</v>
+        <v>-0.0432</v>
       </c>
       <c r="G9">
-        <v>0.3162790697674419</v>
+        <v>0.1206990715456035</v>
       </c>
       <c r="H9">
-        <v>0.3162790697674419</v>
+        <v>0.1206990715456035</v>
       </c>
       <c r="I9">
-        <v>0.3465034966538884</v>
+        <v>0.07190272078688403</v>
       </c>
       <c r="J9">
-        <v>0.2678588828066014</v>
+        <v>0.03732529773331878</v>
       </c>
       <c r="K9">
-        <v>3.44</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L9">
-        <v>0.2666666666666667</v>
+        <v>0.04385581649371928</v>
       </c>
       <c r="M9">
-        <v>2.71</v>
+        <v>13.65</v>
       </c>
       <c r="N9">
-        <v>0.2022388059701492</v>
+        <v>0.3130733944954128</v>
       </c>
       <c r="O9">
-        <v>0.7877906976744186</v>
+        <v>1.699875466998755</v>
       </c>
       <c r="P9">
-        <v>2.71</v>
+        <v>6.8</v>
       </c>
       <c r="Q9">
-        <v>0.2022388059701492</v>
+        <v>0.1559633027522936</v>
       </c>
       <c r="R9">
-        <v>0.7877906976744186</v>
+        <v>0.8468244084682441</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>6.849999999999999</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.5018315018315018</v>
       </c>
       <c r="U9">
-        <v>4.55</v>
+        <v>43.7</v>
       </c>
       <c r="V9">
-        <v>0.3395522388059701</v>
+        <v>1.002293577981651</v>
       </c>
       <c r="W9">
-        <v>0.129811320754717</v>
+        <v>0.05983606557377049</v>
       </c>
       <c r="X9">
-        <v>0.1029346578723503</v>
+        <v>0.1719313508664606</v>
       </c>
       <c r="Y9">
-        <v>0.02687666288236665</v>
+        <v>-0.1120952852926901</v>
       </c>
       <c r="Z9">
-        <v>0.5413452550637723</v>
+        <v>2.673068439505426</v>
       </c>
       <c r="AA9">
-        <v>0.1450041352340367</v>
+        <v>0.09977307536607782</v>
       </c>
       <c r="AB9">
-        <v>0.1011098162597825</v>
+        <v>0.1700085560455271</v>
       </c>
       <c r="AC9">
-        <v>0.04389431897425426</v>
+        <v>-0.07023548067944924</v>
       </c>
       <c r="AD9">
-        <v>0.48</v>
+        <v>0.288</v>
       </c>
       <c r="AE9">
-        <v>0.06052446582419566</v>
+        <v>0.8880591196076675</v>
       </c>
       <c r="AF9">
-        <v>0.5405244658241957</v>
+        <v>1.176059119607668</v>
       </c>
       <c r="AG9">
-        <v>-4.009475534175804</v>
+        <v>-42.52394088039234</v>
       </c>
       <c r="AH9">
-        <v>0.03877361050147825</v>
+        <v>0.0262653556997084</v>
       </c>
       <c r="AI9">
-        <v>0.0199157708431476</v>
+        <v>0.01026444030842396</v>
       </c>
       <c r="AJ9">
-        <v>-0.4269703517378459</v>
+        <v>-39.51821986871575</v>
       </c>
       <c r="AK9">
-        <v>-0.1774848361861404</v>
+        <v>-0.5999760907788424</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="AM9">
-        <v>-0.004</v>
+        <v>0.312</v>
       </c>
       <c r="AN9">
-        <v>0.09463722397476342</v>
+        <v>0.01966810079901659</v>
+      </c>
+      <c r="AO9">
+        <v>41.66666666666666</v>
       </c>
       <c r="AP9">
-        <v>-0.7905117378106871</v>
+        <v>-2.904045679190899</v>
       </c>
       <c r="AQ9">
-        <v>-1107.5</v>
+        <v>41.66666666666666</v>
       </c>
     </row>
     <row r="10">
@@ -1642,7 +1645,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reliance Insurance Company Limited (KASE:RICL)</t>
+          <t>Shaheen Insurance Company Limited (KASE:SHNI)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1651,28 +1654,28 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.007940000000000001</v>
+        <v>-0.007980000000000001</v>
       </c>
       <c r="E10">
-        <v>0.00139</v>
+        <v>0.00528</v>
       </c>
       <c r="G10">
-        <v>0.2298449612403101</v>
+        <v>0.05037593984962406</v>
       </c>
       <c r="H10">
-        <v>0.2298449612403101</v>
+        <v>0.05037593984962406</v>
       </c>
       <c r="I10">
-        <v>0.2128085609138944</v>
+        <v>0.1857142857142857</v>
       </c>
       <c r="J10">
-        <v>0.1577784990500845</v>
+        <v>0.1416847590099869</v>
       </c>
       <c r="K10">
-        <v>0.41</v>
+        <v>0.251</v>
       </c>
       <c r="L10">
-        <v>0.1589147286821705</v>
+        <v>0.1887218045112782</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1696,67 +1699,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="V10">
-        <v>0.5024390243902439</v>
+        <v>2.314465408805031</v>
       </c>
       <c r="W10">
-        <v>0.06984667802385008</v>
+        <v>0.06338383838383839</v>
       </c>
       <c r="X10">
-        <v>0.1009259282541355</v>
+        <v>0.1784126530671023</v>
       </c>
       <c r="Y10">
-        <v>-0.03107925023028539</v>
+        <v>-0.1150288146832639</v>
       </c>
       <c r="Z10">
-        <v>0.5495477391836002</v>
+        <v>0.6974305191400105</v>
       </c>
       <c r="AA10">
-        <v>0.08670681744475575</v>
+        <v>0.09881527503056249</v>
       </c>
       <c r="AB10">
-        <v>0.1006270946321099</v>
+        <v>0.17185875175732</v>
       </c>
       <c r="AC10">
-        <v>-0.01392027718735414</v>
+        <v>-0.07304347672675747</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="AE10">
-        <v>0.0147695642107621</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.0147695642107621</v>
+        <v>0.077</v>
       </c>
       <c r="AG10">
-        <v>-1.015230435789238</v>
+        <v>-1.763</v>
       </c>
       <c r="AH10">
-        <v>0.00715312956310823</v>
+        <v>0.08830275229357798</v>
       </c>
       <c r="AI10">
-        <v>0.002411448146076546</v>
+        <v>0.02342561606327959</v>
       </c>
       <c r="AJ10">
-        <v>-0.9811174109702125</v>
+        <v>1.821280991735537</v>
       </c>
       <c r="AK10">
-        <v>-0.1992691569253552</v>
+        <v>-1.218382861091915</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>0.2950191570881226</v>
+      </c>
+      <c r="AO10">
+        <v>41.16666666666666</v>
       </c>
       <c r="AP10">
-        <v>-1.656167105692068</v>
+        <v>-6.754789272030652</v>
+      </c>
+      <c r="AQ10">
+        <v>41.16666666666666</v>
       </c>
     </row>
     <row r="11">
@@ -1767,7 +1776,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Habib Insurance Company Limited (KASE:HICL)</t>
+          <t>Crescent Star Insurance Limited (KASE:CSIL)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1776,121 +1785,109 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.07490000000000001</v>
-      </c>
-      <c r="E11">
-        <v>-0.079</v>
+        <v>-0.161</v>
       </c>
       <c r="G11">
-        <v>0.1269026548672566</v>
+        <v>0.3914728682170542</v>
       </c>
       <c r="H11">
-        <v>0.1269026548672566</v>
+        <v>0.3914728682170542</v>
       </c>
       <c r="I11">
-        <v>0.1734513274336283</v>
+        <v>0.3811369509043928</v>
       </c>
       <c r="J11">
-        <v>0.1191307173302242</v>
+        <v>0.3266888150609081</v>
       </c>
       <c r="K11">
-        <v>0.636</v>
+        <v>0.265</v>
       </c>
       <c r="L11">
-        <v>0.1125663716814159</v>
+        <v>0.3423772609819122</v>
       </c>
       <c r="M11">
-        <v>0.356</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.07280163599182005</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.559748427672956</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>0.356</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.07280163599182005</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.559748427672956</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>0.168</v>
+        <v>0.014</v>
       </c>
       <c r="V11">
-        <v>0.0343558282208589</v>
+        <v>0.01886792452830189</v>
       </c>
       <c r="W11">
-        <v>0.08548387096774193</v>
+        <v>0.05824175824175825</v>
       </c>
       <c r="X11">
-        <v>0.118714216178893</v>
+        <v>0.1694296081871153</v>
       </c>
       <c r="Y11">
-        <v>-0.03323034521115106</v>
+        <v>-0.1111878499453571</v>
       </c>
       <c r="Z11">
-        <v>0.6633012444235737</v>
+        <v>0.177319587628866</v>
       </c>
       <c r="AA11">
-        <v>0.07901955305421071</v>
+        <v>0.05792832596956308</v>
       </c>
       <c r="AB11">
-        <v>0.1041890516857991</v>
+        <v>0.1694296081871153</v>
       </c>
       <c r="AC11">
-        <v>-0.02516949863158843</v>
+        <v>-0.1115012822175523</v>
       </c>
       <c r="AD11">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>1.302</v>
+        <v>-0.014</v>
       </c>
       <c r="AH11">
-        <v>0.2311320754716981</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>0.1693548387096774</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>0.2102713178294574</v>
+        <v>-0.01923076923076923</v>
       </c>
       <c r="AK11">
-        <v>0.1529605263157895</v>
+        <v>-0.004004576659038902</v>
       </c>
       <c r="AL11">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AN11">
-        <v>1.582346609257266</v>
-      </c>
-      <c r="AO11">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.401506996770721</v>
-      </c>
-      <c r="AQ11">
-        <v>14</v>
+        <v>-0.04034582132564842</v>
       </c>
     </row>
     <row r="12">
@@ -1901,7 +1898,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Crescent Star Insurance Limited (KASE:CSIL)</t>
+          <t>Habib Insurance Company Limited (KASE:HICL)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1910,115 +1907,121 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.107</v>
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="E12">
+        <v>-0.05429999999999999</v>
       </c>
       <c r="G12">
-        <v>0.4988584474885845</v>
+        <v>0.1248148148148148</v>
       </c>
       <c r="H12">
-        <v>0.4988584474885845</v>
+        <v>0.1248148148148148</v>
       </c>
       <c r="I12">
-        <v>0.2979371452280111</v>
+        <v>0.07925925925925925</v>
       </c>
       <c r="J12">
-        <v>0.1901726458902199</v>
+        <v>0.05962403491104398</v>
       </c>
       <c r="K12">
-        <v>0.194</v>
+        <v>0.498</v>
       </c>
       <c r="L12">
-        <v>0.2214611872146119</v>
+        <v>0.09222222222222222</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>0.326</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.09939024390243903</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0.6546184738955824</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>0.326</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.09939024390243903</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0.6546184738955824</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
       <c r="U12">
-        <v>0.016</v>
+        <v>2.47</v>
       </c>
       <c r="V12">
-        <v>0.0128</v>
+        <v>0.753048780487805</v>
       </c>
       <c r="W12">
-        <v>0.04340044742729307</v>
+        <v>0.06907073509015256</v>
       </c>
       <c r="X12">
-        <v>0.1012183638556133</v>
+        <v>0.1735579817190289</v>
       </c>
       <c r="Y12">
-        <v>-0.05781791642832027</v>
+        <v>-0.1044872466288763</v>
       </c>
       <c r="Z12">
-        <v>0.2045278494907743</v>
+        <v>0.6343984962406015</v>
       </c>
       <c r="AA12">
-        <v>0.0388956022958972</v>
+        <v>0.03782539808736343</v>
       </c>
       <c r="AB12">
-        <v>0.1007183611035105</v>
+        <v>0.1703689456910383</v>
       </c>
       <c r="AC12">
-        <v>-0.06182275880761325</v>
+        <v>-0.1325435476036749</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="AE12">
-        <v>0.01503530390131134</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.01503530390131134</v>
+        <v>0.146</v>
       </c>
       <c r="AG12">
-        <v>-0.0009646960986886589</v>
+        <v>-2.324</v>
       </c>
       <c r="AH12">
-        <v>0.01188528403511202</v>
+        <v>0.04261529480443666</v>
       </c>
       <c r="AI12">
-        <v>0.003436613160105026</v>
+        <v>0.02762012864169505</v>
       </c>
       <c r="AJ12">
-        <v>-0.000772352947651255</v>
+        <v>-2.430962343096236</v>
       </c>
       <c r="AK12">
-        <v>-0.0002213095401694181</v>
+        <v>-0.8252840909090912</v>
       </c>
       <c r="AL12">
-        <v>0.001</v>
+        <v>0.023</v>
       </c>
       <c r="AM12">
-        <v>0.001</v>
+        <v>0.023</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AO12">
-        <v>251</v>
+        <v>18.60869565217391</v>
       </c>
       <c r="AP12">
-        <v>-0.002780104030803051</v>
+        <v>-5.305936073059361</v>
       </c>
       <c r="AQ12">
-        <v>251</v>
+        <v>18.60869565217391</v>
       </c>
     </row>
     <row r="13">
@@ -2029,7 +2032,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shaheen Insurance Company Limited (KASE:SHNI)</t>
+          <t>Reliance Insurance Company Limited (KASE:RICL)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2038,118 +2041,115 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.0372</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="E13">
-        <v>-0.111</v>
+        <v>0.0699</v>
       </c>
       <c r="G13">
-        <v>0.1413533834586466</v>
+        <v>0.2557471264367816</v>
       </c>
       <c r="H13">
-        <v>0.1413533834586466</v>
+        <v>0.2557471264367816</v>
       </c>
       <c r="I13">
-        <v>-0.01428571428571429</v>
+        <v>0.1393277846988615</v>
       </c>
       <c r="J13">
-        <v>-0.01428571428571429</v>
+        <v>0.09806762528160211</v>
       </c>
       <c r="K13">
-        <v>0.13</v>
+        <v>0.163</v>
       </c>
       <c r="L13">
-        <v>0.09774436090225563</v>
+        <v>0.09367816091954023</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>0.127</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.0675531914893617</v>
       </c>
       <c r="O13">
-        <v>-0</v>
+        <v>0.7791411042944785</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>0.127</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.0675531914893617</v>
       </c>
       <c r="R13">
-        <v>-0</v>
+        <v>0.7791411042944785</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
       <c r="U13">
-        <v>2.26</v>
+        <v>0.639</v>
       </c>
       <c r="V13">
-        <v>1.558620689655172</v>
+        <v>0.3398936170212766</v>
       </c>
       <c r="W13">
-        <v>0.03299492385786802</v>
+        <v>0.02667757774140753</v>
       </c>
       <c r="X13">
-        <v>0.1091440612011928</v>
+        <v>0.1698167911436287</v>
       </c>
       <c r="Y13">
-        <v>-0.0761491373433248</v>
+        <v>-0.1431392134022211</v>
       </c>
       <c r="Z13">
-        <v>0.7907253269916766</v>
+        <v>0.3419913304397774</v>
       </c>
       <c r="AA13">
-        <v>-0.01129607609988109</v>
+        <v>0.03353827764312466</v>
       </c>
       <c r="AB13">
-        <v>0.1028984877525343</v>
+        <v>0.1695439712990963</v>
       </c>
       <c r="AC13">
-        <v>-0.1141945638524154</v>
+        <v>-0.1360056936559716</v>
       </c>
       <c r="AD13">
-        <v>0.207</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>0.007848273119904572</v>
       </c>
       <c r="AF13">
-        <v>0.207</v>
+        <v>0.007848273119904572</v>
       </c>
       <c r="AG13">
-        <v>-2.053</v>
+        <v>-0.6311517268800955</v>
       </c>
       <c r="AH13">
-        <v>0.1249245624622812</v>
+        <v>0.004157258415123755</v>
       </c>
       <c r="AI13">
-        <v>0.04967602591792657</v>
+        <v>0.001706944782364266</v>
       </c>
       <c r="AJ13">
-        <v>3.404643449419569</v>
+        <v>-0.505387035771236</v>
       </c>
       <c r="AK13">
-        <v>-1.076560041950708</v>
+        <v>-0.1594281173051108</v>
       </c>
       <c r="AL13">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="AN13">
-        <v>-17.25</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP13">
-        <v>171.0833333333333</v>
-      </c>
-      <c r="AQ13">
-        <v>-1</v>
+        <v>-2.125089989495271</v>
       </c>
     </row>
     <row r="14">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Universal Insurance Company Limited (KASE:UVIC)</t>
+          <t>TPL Insurance Limited (KASE:TPLI)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2169,28 +2169,25 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.102</v>
-      </c>
-      <c r="E14">
-        <v>-0.285</v>
+        <v>0.141</v>
       </c>
       <c r="G14">
-        <v>-0.5777777777777777</v>
+        <v>0.02698412698412699</v>
       </c>
       <c r="H14">
-        <v>-0.5777777777777777</v>
+        <v>0.02698412698412699</v>
       </c>
       <c r="I14">
-        <v>-0.5907407407407407</v>
+        <v>-0.005474532011518512</v>
       </c>
       <c r="J14">
-        <v>-0.5907407407407407</v>
+        <v>-0.005474532011518512</v>
       </c>
       <c r="K14">
-        <v>0.07000000000000001</v>
+        <v>-0.358</v>
       </c>
       <c r="L14">
-        <v>0.1296296296296296</v>
+        <v>-0.02841269841269841</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2199,7 +2196,7 @@
         <v>-0</v>
       </c>
       <c r="O14">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14">
         <v>-0</v>
@@ -2208,73 +2205,79 @@
         <v>-0</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
       <c r="U14">
-        <v>0.03</v>
+        <v>6.42</v>
       </c>
       <c r="V14">
-        <v>0.02521008403361345</v>
+        <v>0.436734693877551</v>
       </c>
       <c r="W14">
-        <v>0.01425661914460285</v>
+        <v>-0.03891304347826087</v>
       </c>
       <c r="X14">
-        <v>0.1004891361401464</v>
+        <v>0.1766846683620988</v>
       </c>
       <c r="Y14">
-        <v>-0.08623251699554355</v>
+        <v>-0.2155977118403596</v>
       </c>
       <c r="Z14">
-        <v>0.1118939079983423</v>
+        <v>3.157977432536949</v>
       </c>
       <c r="AA14">
-        <v>-0.06610029009531702</v>
+        <v>-0.01728844854607657</v>
       </c>
       <c r="AB14">
-        <v>0.1004891361401464</v>
+        <v>0.1716211176135785</v>
       </c>
       <c r="AC14">
-        <v>-0.1665894262354634</v>
+        <v>-0.188909566159655</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>0.04989551672566622</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.149895516725666</v>
       </c>
       <c r="AG14">
-        <v>-0.03</v>
+        <v>-5.270104483274333</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.0725490912865788</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>0.1129574969444801</v>
       </c>
       <c r="AJ14">
-        <v>-0.02586206896551724</v>
+        <v>-0.55887199109755</v>
       </c>
       <c r="AK14">
-        <v>-0.006237006237006237</v>
+        <v>-1.401662482329787</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="AN14">
-        <v>-0</v>
+        <v>-14.28571428571429</v>
+      </c>
+      <c r="AO14">
+        <v>-0.6862745098039216</v>
       </c>
       <c r="AP14">
-        <v>0.1003344481605351</v>
+        <v>68.44291536719913</v>
+      </c>
+      <c r="AQ14">
+        <v>-0.6862745098039216</v>
       </c>
     </row>
     <row r="15">
@@ -2285,7 +2288,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Pakistan General Insurance Company Limited (KASE:PKGI)</t>
+          <t>The Universal Insurance Company Limited (KASE:UVIC)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2294,25 +2297,25 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.534</v>
+        <v>0.114</v>
       </c>
       <c r="G15">
-        <v>-4.685714285714285</v>
+        <v>-0.6675126903553299</v>
       </c>
       <c r="H15">
-        <v>-4.685714285714285</v>
+        <v>-0.6675126903553299</v>
       </c>
       <c r="I15">
-        <v>-6.6</v>
+        <v>-0.9314720812182741</v>
       </c>
       <c r="J15">
-        <v>-6.6</v>
+        <v>-0.9314720812182741</v>
       </c>
       <c r="K15">
-        <v>-0.268</v>
+        <v>-0.099</v>
       </c>
       <c r="L15">
-        <v>-7.657142857142857</v>
+        <v>-0.2512690355329949</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2336,31 +2339,31 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>0.005</v>
+        <v>0.183</v>
       </c>
       <c r="V15">
-        <v>0.005482456140350877</v>
+        <v>0.1869254341164454</v>
       </c>
       <c r="W15">
-        <v>-0.09675090252707581</v>
+        <v>-0.02045454545454545</v>
       </c>
       <c r="X15">
-        <v>0.1004891361401464</v>
+        <v>0.1694296081871153</v>
       </c>
       <c r="Y15">
-        <v>-0.1972400386672222</v>
+        <v>-0.1898841536416608</v>
       </c>
       <c r="Z15">
-        <v>0.01264907842428623</v>
+        <v>0.08191268191268192</v>
       </c>
       <c r="AA15">
-        <v>-0.08348391760028913</v>
+        <v>-0.0762993762993763</v>
       </c>
       <c r="AB15">
-        <v>0.1004891361401464</v>
+        <v>0.1694296081871153</v>
       </c>
       <c r="AC15">
-        <v>-0.1839730537404355</v>
+        <v>-0.2457289844864916</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -2372,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>-0.005</v>
+        <v>-0.183</v>
       </c>
       <c r="AH15">
         <v>0</v>
@@ -2381,10 +2384,10 @@
         <v>0</v>
       </c>
       <c r="AJ15">
-        <v>-0.005512679162072767</v>
+        <v>-0.2298994974874372</v>
       </c>
       <c r="AK15">
-        <v>-0.002070393374741201</v>
+        <v>-0.05706267539756781</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2396,7 +2399,7 @@
         <v>-0</v>
       </c>
       <c r="AP15">
-        <v>0.04273504273504274</v>
+        <v>0.5169491525423729</v>
       </c>
     </row>
     <row r="16">
@@ -2407,7 +2410,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Premier Insurance Limited (KASE:PINL)</t>
+          <t>The Pakistan General Insurance Company Limited (KASE:PKGI)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2416,25 +2419,28 @@
         </is>
       </c>
       <c r="D16">
-        <v>-0.124</v>
+        <v>-0.54</v>
+      </c>
+      <c r="E16">
+        <v>-0.182</v>
       </c>
       <c r="G16">
-        <v>-0.3702040816326531</v>
+        <v>-8.653846153846155</v>
       </c>
       <c r="H16">
-        <v>-0.3702040816326531</v>
+        <v>-8.653846153846155</v>
       </c>
       <c r="I16">
-        <v>-0.2538775510204082</v>
+        <v>-8.153846153846153</v>
       </c>
       <c r="J16">
-        <v>-0.2538775510204082</v>
+        <v>-8.153846153846153</v>
       </c>
       <c r="K16">
-        <v>-0.221</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L16">
-        <v>-0.09020408163265306</v>
+        <v>3.230769230769231</v>
       </c>
       <c r="M16">
         <v>-0</v>
@@ -2443,7 +2449,7 @@
         <v>-0</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P16">
         <v>-0</v>
@@ -2452,79 +2458,73 @@
         <v>-0</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
       <c r="U16">
-        <v>0.453</v>
+        <v>0.002</v>
       </c>
       <c r="V16">
-        <v>0.2664705882352941</v>
+        <v>0.001515151515151515</v>
       </c>
       <c r="W16">
-        <v>-0.03274074074074074</v>
+        <v>0.0347107438016529</v>
       </c>
       <c r="X16">
-        <v>0.1022722622183671</v>
+        <v>0.1694296081871153</v>
       </c>
       <c r="Y16">
-        <v>-0.1350130029591079</v>
+        <v>-0.1347188643854624</v>
       </c>
       <c r="Z16">
-        <v>0.3766333589546503</v>
+        <v>0.01076604554865424</v>
       </c>
       <c r="AA16">
-        <v>-0.09561875480399692</v>
+        <v>-0.08778467908902692</v>
       </c>
       <c r="AB16">
-        <v>0.1011019825706435</v>
+        <v>0.1694296081871153</v>
       </c>
       <c r="AC16">
-        <v>-0.1967207373746405</v>
+        <v>-0.2572142872761423</v>
       </c>
       <c r="AD16">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>-0.403</v>
+        <v>-0.002</v>
       </c>
       <c r="AH16">
-        <v>0.02857142857142857</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>0.006410256410256411</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>-0.3107170393215112</v>
+        <v>-0.001517450682852807</v>
       </c>
       <c r="AK16">
-        <v>-0.0548523206751055</v>
+        <v>-0.001006036217303823</v>
       </c>
       <c r="AL16">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>-0.08547008547008549</v>
-      </c>
-      <c r="AO16">
-        <v>-77.75</v>
+        <v>-0</v>
       </c>
       <c r="AP16">
-        <v>0.688888888888889</v>
-      </c>
-      <c r="AQ16">
-        <v>-77.75</v>
+        <v>0.01136363636363636</v>
       </c>
     </row>
     <row r="17">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TPL Insurance Limited (KASE:TPLI)</t>
+          <t>Premier Insurance Limited (KASE:PINL)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2544,28 +2544,25 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.125</v>
-      </c>
-      <c r="E17">
-        <v>-0.323</v>
+        <v>-0.179</v>
       </c>
       <c r="G17">
-        <v>0.05402777777777778</v>
+        <v>-0.2801470588235294</v>
       </c>
       <c r="H17">
-        <v>0.05402777777777778</v>
+        <v>-0.2801470588235294</v>
       </c>
       <c r="I17">
-        <v>0.01717120074190354</v>
+        <v>-0.575</v>
       </c>
       <c r="J17">
-        <v>0.008585600370951768</v>
+        <v>-0.575</v>
       </c>
       <c r="K17">
-        <v>0.089</v>
+        <v>-0.599</v>
       </c>
       <c r="L17">
-        <v>0.006180555555555555</v>
+        <v>-0.4404411764705882</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2574,7 +2571,7 @@
         <v>-0</v>
       </c>
       <c r="O17">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <v>-0</v>
@@ -2583,79 +2580,79 @@
         <v>-0</v>
       </c>
       <c r="R17">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="U17">
-        <v>6.59</v>
+        <v>0.262</v>
       </c>
       <c r="V17">
-        <v>0.334517766497462</v>
+        <v>0.1884892086330935</v>
       </c>
       <c r="W17">
-        <v>0.01812627291242363</v>
+        <v>-0.07729032258064515</v>
       </c>
       <c r="X17">
-        <v>0.1048858453776077</v>
+        <v>0.1718984138037164</v>
       </c>
       <c r="Y17">
-        <v>-0.08675957246518411</v>
+        <v>-0.2491887363843616</v>
       </c>
       <c r="Z17">
-        <v>-19.69024904366218</v>
+        <v>0.1851095685313734</v>
       </c>
       <c r="AA17">
-        <v>-0.1690526094933988</v>
+        <v>-0.1064380019055397</v>
       </c>
       <c r="AB17">
-        <v>0.1017932428138338</v>
+        <v>0.1702128378319891</v>
       </c>
       <c r="AC17">
-        <v>-0.2708458523072326</v>
+        <v>-0.2766508397375288</v>
       </c>
       <c r="AD17">
-        <v>1.33</v>
+        <v>0.037</v>
       </c>
       <c r="AE17">
-        <v>0.09867354658294551</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.428673546582946</v>
+        <v>0.037</v>
       </c>
       <c r="AG17">
-        <v>-5.161326453417054</v>
+        <v>-0.225</v>
       </c>
       <c r="AH17">
-        <v>0.06761775856080654</v>
+        <v>0.02592852137351086</v>
       </c>
       <c r="AI17">
-        <v>0.1344169185666875</v>
+        <v>0.008137233340664175</v>
       </c>
       <c r="AJ17">
-        <v>-0.3550066955475544</v>
+        <v>-0.1931330472103005</v>
       </c>
       <c r="AK17">
-        <v>-1.277975650640039</v>
+        <v>-0.05250875145857643</v>
       </c>
       <c r="AL17">
-        <v>0.105</v>
+        <v>0.006</v>
       </c>
       <c r="AM17">
-        <v>0.105</v>
+        <v>0.006</v>
       </c>
       <c r="AN17">
-        <v>3.821839080459771</v>
+        <v>-0.05027173913043478</v>
       </c>
       <c r="AO17">
-        <v>2.057142857142857</v>
+        <v>-130.3333333333333</v>
       </c>
       <c r="AP17">
-        <v>-14.83139785464671</v>
+        <v>0.3057065217391304</v>
       </c>
       <c r="AQ17">
-        <v>2.057142857142857</v>
+        <v>-130.3333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/pakistan/pakistan_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_insurance_prop_cas.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0541</v>
+        <v>0.11</v>
       </c>
       <c r="E2">
-        <v>0.00772</v>
+        <v>0.186</v>
       </c>
       <c r="G2">
-        <v>0.1620248697883164</v>
+        <v>0.1093897725376786</v>
       </c>
       <c r="H2">
-        <v>0.1620248697883164</v>
+        <v>0.1093897725376786</v>
       </c>
       <c r="I2">
-        <v>0.1028183466268026</v>
+        <v>0.1167562558254991</v>
       </c>
       <c r="J2">
-        <v>0.07872003834097216</v>
+        <v>0.08859989405205235</v>
       </c>
       <c r="K2">
-        <v>31.825</v>
+        <v>39.045</v>
       </c>
       <c r="L2">
-        <v>0.05848958122746336</v>
+        <v>0.06785808631333073</v>
       </c>
       <c r="M2">
-        <v>36.556</v>
+        <v>25.099</v>
       </c>
       <c r="N2">
-        <v>0.169001322200956</v>
+        <v>0.1257609844821798</v>
       </c>
       <c r="O2">
-        <v>1.14865671641791</v>
+        <v>0.6428223844282238</v>
       </c>
       <c r="P2">
-        <v>29.706</v>
+        <v>25.099</v>
       </c>
       <c r="Q2">
-        <v>0.137333222379407</v>
+        <v>0.1257609844821798</v>
       </c>
       <c r="R2">
-        <v>0.9334171249018067</v>
+        <v>0.6428223844282238</v>
       </c>
       <c r="S2">
-        <v>6.849999999999999</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.1873837400153189</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>117.78</v>
+        <v>103.044</v>
       </c>
       <c r="V2">
-        <v>0.5445063937200078</v>
+        <v>0.5163119998797457</v>
       </c>
       <c r="W2">
-        <v>0.06338383838383839</v>
+        <v>0.09100817438692099</v>
       </c>
       <c r="X2">
-        <v>0.1719313508664606</v>
+        <v>0.1673098168581672</v>
       </c>
       <c r="Y2">
-        <v>-0.1085475124826222</v>
+        <v>-0.07630164247124621</v>
       </c>
       <c r="Z2">
-        <v>1.806466447994428</v>
+        <v>2.540777952999839</v>
       </c>
       <c r="AA2">
-        <v>0.09881527503056249</v>
+        <v>0.1367962851684956</v>
       </c>
       <c r="AB2">
-        <v>0.1700472069062335</v>
+        <v>0.1663472750141894</v>
       </c>
       <c r="AC2">
-        <v>-0.07304347672675747</v>
+        <v>-0.02955098984569379</v>
       </c>
       <c r="AD2">
-        <v>7.037</v>
+        <v>4.594</v>
       </c>
       <c r="AE2">
-        <v>1.175490717519515</v>
+        <v>1.021922240272024</v>
       </c>
       <c r="AF2">
-        <v>8.212490717519515</v>
+        <v>5.615922240272024</v>
       </c>
       <c r="AG2">
-        <v>-109.5675092824805</v>
+        <v>-97.42807775972798</v>
       </c>
       <c r="AH2">
-        <v>0.03657823768222348</v>
+        <v>0.02736898611783511</v>
       </c>
       <c r="AI2">
-        <v>0.02262503268762527</v>
+        <v>0.01834513784123189</v>
       </c>
       <c r="AJ2">
-        <v>-1.026504202429168</v>
+        <v>-0.9537846863480381</v>
       </c>
       <c r="AK2">
-        <v>-0.4468450094526383</v>
+        <v>-0.479747663824346</v>
       </c>
       <c r="AL2">
-        <v>0.743</v>
+        <v>0.536</v>
       </c>
       <c r="AM2">
-        <v>0.743</v>
+        <v>0.536</v>
       </c>
       <c r="AN2">
-        <v>0.1135073230531002</v>
+        <v>0.06255105931049507</v>
       </c>
       <c r="AO2">
-        <v>74.92462987886945</v>
+        <v>124.8563432835821</v>
       </c>
       <c r="AP2">
-        <v>-1.767331913066657</v>
+        <v>-1.326562792872501</v>
       </c>
       <c r="AQ2">
-        <v>74.92462987886945</v>
+        <v>124.8563432835821</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The United Insurance Company of Pakistan Limited (KASE:UNIC)</t>
+          <t>Atlas Insurance Limited (KASE:ATIL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.04650000000000001</v>
+        <v>0.122</v>
       </c>
       <c r="E3">
-        <v>0.349</v>
+        <v>0.08</v>
       </c>
       <c r="G3">
-        <v>0.4213836477987422</v>
+        <v>0.4807692307692307</v>
       </c>
       <c r="H3">
-        <v>0.4213836477987422</v>
+        <v>0.4807692307692307</v>
       </c>
       <c r="I3">
-        <v>0.313829747125526</v>
+        <v>0.5577406941138842</v>
       </c>
       <c r="J3">
-        <v>0.2403258348659832</v>
+        <v>0.3354383533994534</v>
       </c>
       <c r="K3">
-        <v>3.76</v>
+        <v>3.37</v>
       </c>
       <c r="L3">
-        <v>0.2364779874213836</v>
+        <v>0.3240384615384616</v>
       </c>
       <c r="M3">
-        <v>3.14</v>
+        <v>2.74</v>
       </c>
       <c r="N3">
-        <v>0.3165322580645161</v>
+        <v>0.1234234234234234</v>
       </c>
       <c r="O3">
-        <v>0.8351063829787235</v>
+        <v>0.8130563798219584</v>
       </c>
       <c r="P3">
-        <v>3.14</v>
+        <v>2.74</v>
       </c>
       <c r="Q3">
-        <v>0.3165322580645161</v>
+        <v>0.1234234234234234</v>
       </c>
       <c r="R3">
-        <v>0.8351063829787235</v>
+        <v>0.8130563798219584</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.05</v>
+        <v>5.69</v>
       </c>
       <c r="V3">
-        <v>0.3074596774193548</v>
+        <v>0.2563063063063064</v>
       </c>
       <c r="W3">
-        <v>0.1413533834586466</v>
+        <v>0.2067484662576687</v>
       </c>
       <c r="X3">
-        <v>0.1732866043811476</v>
+        <v>0.1670093106736395</v>
       </c>
       <c r="Y3">
-        <v>-0.03193322092250098</v>
+        <v>0.03973915558402921</v>
       </c>
       <c r="Z3">
-        <v>0.7053958536022743</v>
+        <v>0.9152928255798743</v>
       </c>
       <c r="AA3">
-        <v>0.1695248474279695</v>
+        <v>0.3070243182908461</v>
       </c>
       <c r="AB3">
-        <v>0.1703096639379897</v>
+        <v>0.1663083430221221</v>
       </c>
       <c r="AC3">
-        <v>-0.0007848165100202142</v>
+        <v>0.140715975268724</v>
       </c>
       <c r="AD3">
-        <v>0.402</v>
+        <v>0.283</v>
       </c>
       <c r="AE3">
-        <v>0.01053510352068179</v>
+        <v>0.02248390607802209</v>
       </c>
       <c r="AF3">
-        <v>0.4125351035206818</v>
+        <v>0.3054839060780221</v>
       </c>
       <c r="AG3">
-        <v>-2.637464896479318</v>
+        <v>-5.384516093921978</v>
       </c>
       <c r="AH3">
-        <v>0.03992583614645699</v>
+        <v>0.01357375417266725</v>
       </c>
       <c r="AI3">
-        <v>0.02114205567508485</v>
+        <v>0.02313310956650506</v>
       </c>
       <c r="AJ3">
-        <v>-0.3621630186450124</v>
+        <v>-0.3202117836154405</v>
       </c>
       <c r="AK3">
-        <v>-0.1602101304503988</v>
+        <v>-0.7164563401655801</v>
       </c>
       <c r="AL3">
-        <v>0.04</v>
+        <v>0.176</v>
       </c>
       <c r="AM3">
-        <v>0.04</v>
+        <v>0.176</v>
       </c>
       <c r="AN3">
-        <v>0.07319737800437</v>
+        <v>0.0476832350463353</v>
       </c>
       <c r="AO3">
-        <v>124.5</v>
+        <v>32.89772727272727</v>
       </c>
       <c r="AP3">
-        <v>-0.48023759950461</v>
+        <v>-0.9072478675521447</v>
       </c>
       <c r="AQ3">
-        <v>124.5</v>
+        <v>32.89772727272727</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Atlas Insurance Limited (KASE:ATIL)</t>
+          <t>TPL Insurance Limited (KASE:TPLI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0541</v>
+        <v>0.187</v>
       </c>
       <c r="E4">
-        <v>0.00772</v>
+        <v>3.63</v>
       </c>
       <c r="G4">
-        <v>0.7014314928425359</v>
+        <v>0.0359016393442623</v>
       </c>
       <c r="H4">
-        <v>0.7014314928425359</v>
+        <v>0.0359016393442623</v>
       </c>
       <c r="I4">
-        <v>0.4871204328993705</v>
+        <v>0.08496915115526817</v>
       </c>
       <c r="J4">
-        <v>0.3115908952447999</v>
+        <v>0.08166186328421425</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>4.65</v>
       </c>
       <c r="L4">
-        <v>0.3067484662576687</v>
+        <v>0.3811475409836066</v>
       </c>
       <c r="M4">
-        <v>2.57</v>
+        <v>1.18</v>
       </c>
       <c r="N4">
-        <v>0.1122270742358079</v>
+        <v>0.1145631067961165</v>
       </c>
       <c r="O4">
-        <v>0.8566666666666666</v>
+        <v>0.253763440860215</v>
       </c>
       <c r="P4">
-        <v>2.57</v>
+        <v>1.18</v>
       </c>
       <c r="Q4">
-        <v>0.1122270742358079</v>
+        <v>0.1145631067961165</v>
       </c>
       <c r="R4">
-        <v>0.8566666666666666</v>
+        <v>0.253763440860215</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5.28</v>
+        <v>11.5</v>
       </c>
       <c r="V4">
-        <v>0.2305676855895197</v>
+        <v>1.116504854368932</v>
       </c>
       <c r="W4">
-        <v>0.1209677419354839</v>
+        <v>0.5149501661129569</v>
       </c>
       <c r="X4">
-        <v>0.1710286269109225</v>
+        <v>0.1693386988012014</v>
       </c>
       <c r="Y4">
-        <v>-0.05006088497543869</v>
+        <v>0.3456114673117555</v>
       </c>
       <c r="Z4">
-        <v>0.46801399883413</v>
+        <v>3.282321236901742</v>
       </c>
       <c r="AA4">
-        <v>0.1458289008838253</v>
+        <v>0.2680404681027431</v>
       </c>
       <c r="AB4">
-        <v>0.1699415743242982</v>
+        <v>0.1672828579691873</v>
       </c>
       <c r="AC4">
-        <v>-0.02411267344047288</v>
+        <v>0.1007576101335558</v>
       </c>
       <c r="AD4">
-        <v>0.32</v>
+        <v>0.401</v>
       </c>
       <c r="AE4">
-        <v>0.07481083122078888</v>
+        <v>0.006881779528642323</v>
       </c>
       <c r="AF4">
-        <v>0.3948108312207889</v>
+        <v>0.4078817795286424</v>
       </c>
       <c r="AG4">
-        <v>-4.885189168779211</v>
+        <v>-11.09211822047136</v>
       </c>
       <c r="AH4">
-        <v>0.01694844547488856</v>
+        <v>0.03809173354046846</v>
       </c>
       <c r="AI4">
-        <v>0.02364871547286162</v>
+        <v>0.04096069712006056</v>
       </c>
       <c r="AJ4">
-        <v>-0.2711762679357629</v>
+        <v>14.00310955335795</v>
       </c>
       <c r="AK4">
-        <v>-0.4279693497344407</v>
+        <v>7.192780730572647</v>
       </c>
       <c r="AL4">
-        <v>0.039</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AM4">
-        <v>0.039</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AN4">
-        <v>0.06531945294958155</v>
+        <v>0.3790170132325142</v>
       </c>
       <c r="AO4">
-        <v>121.2820512820513</v>
+        <v>12.26190476190476</v>
       </c>
       <c r="AP4">
-        <v>-0.9971808876871222</v>
+        <v>-10.4840436866459</v>
       </c>
       <c r="AQ4">
-        <v>121.2820512820513</v>
+        <v>12.26190476190476</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Century Insurance Company Limited (KASE:CENI)</t>
+          <t>Jubilee General Insurance Company Limited (KASE:JGICL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,46 +990,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.09420000000000001</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="E5">
-        <v>0.105</v>
+        <v>0.186</v>
       </c>
       <c r="G5">
-        <v>0.4065335753176044</v>
+        <v>0.2958579881656805</v>
       </c>
       <c r="H5">
-        <v>0.4065335753176044</v>
+        <v>0.2958579881656805</v>
       </c>
       <c r="I5">
-        <v>0.3357531760435572</v>
+        <v>0.4053254437869823</v>
       </c>
       <c r="J5">
-        <v>0.2146359308634468</v>
+        <v>0.23704550091818</v>
       </c>
       <c r="K5">
-        <v>1.23</v>
+        <v>8.49</v>
       </c>
       <c r="L5">
-        <v>0.2232304900181488</v>
+        <v>0.2511834319526627</v>
       </c>
       <c r="M5">
-        <v>0.493</v>
+        <v>2.38</v>
       </c>
       <c r="N5">
-        <v>0.125765306122449</v>
+        <v>0.0804054054054054</v>
       </c>
       <c r="O5">
-        <v>0.4008130081300813</v>
+        <v>0.2803297997644287</v>
       </c>
       <c r="P5">
-        <v>0.493</v>
+        <v>2.38</v>
       </c>
       <c r="Q5">
-        <v>0.125765306122449</v>
+        <v>0.0804054054054054</v>
       </c>
       <c r="R5">
-        <v>0.4008130081300813</v>
+        <v>0.2803297997644287</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1038,73 +1038,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2.41</v>
+        <v>10.8</v>
       </c>
       <c r="V5">
-        <v>0.614795918367347</v>
+        <v>0.3648648648648649</v>
       </c>
       <c r="W5">
-        <v>0.0984</v>
+        <v>0.1899328859060403</v>
       </c>
       <c r="X5">
-        <v>0.172103183050598</v>
+        <v>0.1657688276676707</v>
       </c>
       <c r="Y5">
-        <v>-0.07370318305059805</v>
+        <v>0.02416405823836959</v>
       </c>
       <c r="Z5">
-        <v>0.6182675044883302</v>
+        <v>1.001422137947381</v>
       </c>
       <c r="AA5">
-        <v>0.132702421348473</v>
+        <v>0.2373826123202916</v>
       </c>
       <c r="AB5">
-        <v>0.1700472069062335</v>
+        <v>0.1657688276676707</v>
       </c>
       <c r="AC5">
-        <v>-0.03734478555776047</v>
+        <v>0.07161378465262092</v>
       </c>
       <c r="AD5">
-        <v>0.113</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.113</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-2.297</v>
+        <v>-10.8</v>
       </c>
       <c r="AH5">
-        <v>0.028018844532606</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.010957044506933</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-1.41528034504005</v>
+        <v>-0.574468085106383</v>
       </c>
       <c r="AK5">
-        <v>-0.2906491205871189</v>
+        <v>-0.3648648648648649</v>
       </c>
       <c r="AL5">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>0.06042780748663101</v>
-      </c>
-      <c r="AO5">
-        <v>92.5</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>-1.228342245989305</v>
-      </c>
-      <c r="AQ5">
-        <v>92.5</v>
+        <v>-0.7826086956521739</v>
       </c>
     </row>
     <row r="6">
@@ -1115,7 +1109,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EFU General Insurance Limited (KASE:EFUG)</t>
+          <t>The United Insurance Company of Pakistan Limited (KASE:UNIC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1124,46 +1118,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.445</v>
+        <v>0.11</v>
       </c>
       <c r="E6">
-        <v>-0.0717</v>
+        <v>0.296</v>
       </c>
       <c r="G6">
-        <v>0.1288600838734273</v>
+        <v>0.48359375</v>
       </c>
       <c r="H6">
-        <v>0.1288600838734273</v>
+        <v>0.48359375</v>
       </c>
       <c r="I6">
-        <v>0.0770110560426992</v>
+        <v>0.38984375</v>
       </c>
       <c r="J6">
-        <v>0.04199954815662021</v>
+        <v>0.2983081105870021</v>
       </c>
       <c r="K6">
-        <v>7.93</v>
+        <v>3.65</v>
       </c>
       <c r="L6">
-        <v>0.03023255813953488</v>
+        <v>0.28515625</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>3.34</v>
       </c>
       <c r="N6">
-        <v>0.1463414634146341</v>
+        <v>0.2854700854700855</v>
       </c>
       <c r="O6">
-        <v>1.513240857503153</v>
+        <v>0.9150684931506849</v>
       </c>
       <c r="P6">
-        <v>12</v>
+        <v>3.34</v>
       </c>
       <c r="Q6">
-        <v>0.1463414634146341</v>
+        <v>0.2854700854700855</v>
       </c>
       <c r="R6">
-        <v>1.513240857503153</v>
+        <v>0.9150684931506849</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1172,73 +1166,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>39.4</v>
+        <v>3.45</v>
       </c>
       <c r="V6">
-        <v>0.4804878048780488</v>
+        <v>0.2948717948717949</v>
       </c>
       <c r="W6">
-        <v>0.06379726468222044</v>
+        <v>0.1910994764397906</v>
       </c>
       <c r="X6">
-        <v>0.173343080083121</v>
+        <v>0.1673098168581672</v>
       </c>
       <c r="Y6">
-        <v>-0.1095458154009006</v>
+        <v>0.02378965958162335</v>
       </c>
       <c r="Z6">
-        <v>3.160621761658031</v>
+        <v>0.7780209093119377</v>
       </c>
       <c r="AA6">
-        <v>0.1327446858836183</v>
+        <v>0.2320899474540254</v>
       </c>
       <c r="AB6">
-        <v>0.1703220283530828</v>
+        <v>0.1664049950948685</v>
       </c>
       <c r="AC6">
-        <v>-0.03757734246946456</v>
+        <v>0.06568495235915689</v>
       </c>
       <c r="AD6">
-        <v>3.46</v>
+        <v>0.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>3.46</v>
+        <v>0.2</v>
       </c>
       <c r="AG6">
-        <v>-35.94</v>
+        <v>-3.25</v>
       </c>
       <c r="AH6">
-        <v>0.04048677743973789</v>
+        <v>0.01680672268907563</v>
       </c>
       <c r="AI6">
-        <v>0.03178394267866985</v>
+        <v>0.01058201058201058</v>
       </c>
       <c r="AJ6">
-        <v>-0.7802865827181936</v>
+        <v>-0.3846153846153846</v>
       </c>
       <c r="AK6">
-        <v>-0.5174200978980708</v>
+        <v>-0.2103559870550162</v>
       </c>
       <c r="AL6">
-        <v>0.047</v>
+        <v>0.03</v>
       </c>
       <c r="AM6">
-        <v>0.047</v>
+        <v>0.03</v>
       </c>
       <c r="AN6">
-        <v>0.1453781512605042</v>
+        <v>0.03603603603603604</v>
       </c>
       <c r="AO6">
-        <v>429.7872340425532</v>
+        <v>166.3333333333333</v>
       </c>
       <c r="AP6">
-        <v>-1.510084033613445</v>
+        <v>-0.5855855855855856</v>
       </c>
       <c r="AQ6">
-        <v>429.7872340425532</v>
+        <v>166.3333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -1249,7 +1243,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jubilee General Insurance Company Limited (KASE:JGICL)</t>
+          <t>EFU General Insurance Limited (KASE:EFUG)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1258,46 +1252,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0393</v>
+        <v>0.341</v>
       </c>
       <c r="E7">
-        <v>0.0249</v>
+        <v>-0.135</v>
       </c>
       <c r="G7">
-        <v>0.3987138263665595</v>
+        <v>0.0831858407079646</v>
       </c>
       <c r="H7">
-        <v>0.3987138263665595</v>
+        <v>0.0831858407079646</v>
       </c>
       <c r="I7">
-        <v>0.280064308681672</v>
+        <v>0.08106194690265486</v>
       </c>
       <c r="J7">
-        <v>0.1764550255735302</v>
+        <v>0.04053097345132743</v>
       </c>
       <c r="K7">
-        <v>6.08</v>
+        <v>4.51</v>
       </c>
       <c r="L7">
-        <v>0.1954983922829582</v>
+        <v>0.0159646017699115</v>
       </c>
       <c r="M7">
-        <v>3.38</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="N7">
-        <v>0.1420168067226891</v>
+        <v>0.1577049180327869</v>
       </c>
       <c r="O7">
-        <v>0.5559210526315789</v>
+        <v>2.133037694013304</v>
       </c>
       <c r="P7">
-        <v>3.38</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q7">
-        <v>0.1420168067226891</v>
+        <v>0.1577049180327869</v>
       </c>
       <c r="R7">
-        <v>0.5559210526315789</v>
+        <v>2.133037694013304</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1306,67 +1300,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>11.1</v>
+        <v>27.3</v>
       </c>
       <c r="V7">
-        <v>0.4663865546218487</v>
+        <v>0.4475409836065574</v>
       </c>
       <c r="W7">
-        <v>0.1064798598949212</v>
+        <v>0.05078828828828829</v>
       </c>
       <c r="X7">
-        <v>0.1700219421079369</v>
+        <v>0.1693156290176004</v>
       </c>
       <c r="Y7">
-        <v>-0.06354208221301573</v>
+        <v>-0.1185273407293121</v>
       </c>
       <c r="Z7">
-        <v>0.6911111111111111</v>
+        <v>5.344305713204692</v>
       </c>
       <c r="AA7">
-        <v>0.121950028785262</v>
+        <v>0.2166099129776769</v>
       </c>
       <c r="AB7">
-        <v>0.1695694889428743</v>
+        <v>0.1670455005478576</v>
       </c>
       <c r="AC7">
-        <v>-0.04761946015761231</v>
+        <v>0.04956441242981929</v>
       </c>
       <c r="AD7">
-        <v>0.152</v>
+        <v>2.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.152</v>
+        <v>2.4</v>
       </c>
       <c r="AG7">
-        <v>-10.948</v>
+        <v>-24.9</v>
       </c>
       <c r="AH7">
-        <v>0.006346025384101536</v>
+        <v>0.03785488958990536</v>
       </c>
       <c r="AI7">
-        <v>0.003388923570855257</v>
+        <v>0.0291970802919708</v>
       </c>
       <c r="AJ7">
-        <v>-0.8518518518518519</v>
+        <v>-0.6897506925207758</v>
       </c>
       <c r="AK7">
-        <v>-0.3243659634984594</v>
+        <v>-0.4535519125683061</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="AN7">
-        <v>0.01729237770193402</v>
+        <v>0.08856088560885608</v>
+      </c>
+      <c r="AO7">
+        <v>497.8260869565217</v>
       </c>
       <c r="AP7">
-        <v>-1.245506257110353</v>
+        <v>-0.9188191881918819</v>
+      </c>
+      <c r="AQ7">
+        <v>497.8260869565217</v>
       </c>
     </row>
     <row r="8">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Askari General Insurance Company Limited (KASE:AGIC)</t>
+          <t>Century Insurance Company Limited (KASE:CENI)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1386,46 +1386,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.152</v>
+        <v>0.186</v>
       </c>
       <c r="E8">
-        <v>0.07980000000000001</v>
+        <v>0.383</v>
       </c>
       <c r="G8">
-        <v>0.2421875</v>
+        <v>0.403254972875226</v>
       </c>
       <c r="H8">
-        <v>0.2421875</v>
+        <v>0.403254972875226</v>
       </c>
       <c r="I8">
-        <v>0.1939946582292999</v>
+        <v>0.4430379746835443</v>
       </c>
       <c r="J8">
-        <v>0.1297644940760695</v>
+        <v>0.2676164608209912</v>
       </c>
       <c r="K8">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="L8">
-        <v>0.12421875</v>
+        <v>0.2694394213381555</v>
       </c>
       <c r="M8">
-        <v>0.87</v>
+        <v>0.479</v>
       </c>
       <c r="N8">
-        <v>0.171259842519685</v>
+        <v>0.1159806295399516</v>
       </c>
       <c r="O8">
-        <v>0.5471698113207547</v>
+        <v>0.3214765100671141</v>
       </c>
       <c r="P8">
-        <v>0.87</v>
+        <v>0.479</v>
       </c>
       <c r="Q8">
-        <v>0.171259842519685</v>
+        <v>0.1159806295399516</v>
       </c>
       <c r="R8">
-        <v>0.5471698113207547</v>
+        <v>0.3214765100671141</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1434,73 +1434,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>0.805</v>
       </c>
       <c r="V8">
-        <v>0.1988188976377953</v>
+        <v>0.1949152542372881</v>
       </c>
       <c r="W8">
-        <v>0.1213740458015267</v>
+        <v>0.146078431372549</v>
       </c>
       <c r="X8">
-        <v>0.1892632643724441</v>
+        <v>0.1678642744700505</v>
       </c>
       <c r="Y8">
-        <v>-0.06788921857091738</v>
+        <v>-0.02178584309750142</v>
       </c>
       <c r="Z8">
-        <v>0.9187256612262141</v>
+        <v>0.6997342781222322</v>
       </c>
       <c r="AA8">
-        <v>0.1192179706237221</v>
+        <v>0.1872604110262029</v>
       </c>
       <c r="AB8">
-        <v>0.1747513069405028</v>
+        <v>0.1666286923965287</v>
       </c>
       <c r="AC8">
-        <v>-0.05553333631678067</v>
+        <v>0.02063171862967417</v>
       </c>
       <c r="AD8">
-        <v>0.9419999999999999</v>
+        <v>0.096</v>
       </c>
       <c r="AE8">
-        <v>0.144341873324806</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.086341873324806</v>
+        <v>0.096</v>
       </c>
       <c r="AG8">
-        <v>0.07634187332480602</v>
+        <v>-0.7090000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.1761728259057855</v>
+        <v>0.02271651680075722</v>
       </c>
       <c r="AI8">
-        <v>0.0954074526665863</v>
+        <v>0.01048492791612058</v>
       </c>
       <c r="AJ8">
-        <v>0.01480543284372664</v>
+        <v>-0.2072493422975738</v>
       </c>
       <c r="AK8">
-        <v>0.007357301277925649</v>
+        <v>-0.08490001197461382</v>
       </c>
       <c r="AL8">
-        <v>0.097</v>
+        <v>0.016</v>
       </c>
       <c r="AM8">
-        <v>0.097</v>
+        <v>0.016</v>
       </c>
       <c r="AN8">
-        <v>0.3764988009592325</v>
+        <v>0.03902439024390244</v>
       </c>
       <c r="AO8">
-        <v>25.36082474226804</v>
+        <v>153.125</v>
       </c>
       <c r="AP8">
-        <v>0.03051233945835572</v>
+        <v>-0.2882113821138212</v>
       </c>
       <c r="AQ8">
-        <v>25.36082474226804</v>
+        <v>153.125</v>
       </c>
     </row>
     <row r="9">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Adamjee Insurance Company Limited (KASE:AICL)</t>
+          <t>Shaheen Insurance Company Limited (KASE:SHNI)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1520,121 +1520,118 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0902</v>
+        <v>0.0658</v>
       </c>
       <c r="E9">
-        <v>-0.0432</v>
+        <v>0.0521</v>
       </c>
       <c r="G9">
-        <v>0.1206990715456035</v>
+        <v>0.121025641025641</v>
       </c>
       <c r="H9">
-        <v>0.1206990715456035</v>
+        <v>0.121025641025641</v>
       </c>
       <c r="I9">
-        <v>0.07190272078688403</v>
+        <v>0.1553846153846154</v>
       </c>
       <c r="J9">
-        <v>0.03732529773331878</v>
+        <v>0.1076923076923077</v>
       </c>
       <c r="K9">
-        <v>8.029999999999999</v>
+        <v>0.281</v>
       </c>
       <c r="L9">
-        <v>0.04385581649371928</v>
+        <v>0.1441025641025641</v>
       </c>
       <c r="M9">
-        <v>13.65</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.3130733944954128</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>1.699875466998755</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>6.8</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.1559633027522936</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.8468244084682441</v>
+        <v>-0</v>
       </c>
       <c r="S9">
-        <v>6.849999999999999</v>
-      </c>
-      <c r="T9">
-        <v>0.5018315018315018</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>43.7</v>
+        <v>0.701</v>
       </c>
       <c r="V9">
-        <v>1.002293577981651</v>
+        <v>0.8029782359679266</v>
       </c>
       <c r="W9">
-        <v>0.05983606557377049</v>
+        <v>0.08753894080996885</v>
       </c>
       <c r="X9">
-        <v>0.1719313508664606</v>
+        <v>0.1719645574026567</v>
       </c>
       <c r="Y9">
-        <v>-0.1120952852926901</v>
+        <v>-0.08442561659268782</v>
       </c>
       <c r="Z9">
-        <v>2.673068439505426</v>
+        <v>1.347615756738079</v>
       </c>
       <c r="AA9">
-        <v>0.09977307536607782</v>
+        <v>0.1451278507256393</v>
       </c>
       <c r="AB9">
-        <v>0.1700085560455271</v>
+        <v>0.1682030374373344</v>
       </c>
       <c r="AC9">
-        <v>-0.07023548067944924</v>
+        <v>-0.02307518671169517</v>
       </c>
       <c r="AD9">
-        <v>0.288</v>
+        <v>0.06</v>
       </c>
       <c r="AE9">
-        <v>0.8880591196076675</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.176059119607668</v>
+        <v>0.06</v>
       </c>
       <c r="AG9">
-        <v>-42.52394088039234</v>
+        <v>-0.641</v>
       </c>
       <c r="AH9">
-        <v>0.0262653556997084</v>
+        <v>0.06430868167202572</v>
       </c>
       <c r="AI9">
-        <v>0.01026444030842396</v>
+        <v>0.02097902097902098</v>
       </c>
       <c r="AJ9">
-        <v>-39.51821986871575</v>
+        <v>-2.762931034482759</v>
       </c>
       <c r="AK9">
-        <v>-0.5999760907788424</v>
+        <v>-0.2968967114404817</v>
       </c>
       <c r="AL9">
-        <v>0.312</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AM9">
-        <v>0.312</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AN9">
-        <v>0.01966810079901659</v>
+        <v>0.1744186046511628</v>
       </c>
       <c r="AO9">
-        <v>41.66666666666666</v>
+        <v>33.66666666666667</v>
       </c>
       <c r="AP9">
-        <v>-2.904045679190899</v>
+        <v>-1.863372093023256</v>
       </c>
       <c r="AQ9">
-        <v>41.66666666666666</v>
+        <v>33.66666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -1645,7 +1642,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shaheen Insurance Company Limited (KASE:SHNI)</t>
+          <t>Adamjee Insurance Company Limited (KASE:AICL)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1654,118 +1651,121 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.007980000000000001</v>
+        <v>0.142</v>
       </c>
       <c r="E10">
-        <v>0.00528</v>
+        <v>0.238</v>
       </c>
       <c r="G10">
-        <v>0.05037593984962406</v>
+        <v>0.06871794871794872</v>
       </c>
       <c r="H10">
-        <v>0.05037593984962406</v>
+        <v>0.06871794871794872</v>
       </c>
       <c r="I10">
-        <v>0.1857142857142857</v>
+        <v>0.06870226273001118</v>
       </c>
       <c r="J10">
-        <v>0.1416847590099869</v>
+        <v>0.04852640835866612</v>
       </c>
       <c r="K10">
-        <v>0.251</v>
+        <v>10.9</v>
       </c>
       <c r="L10">
-        <v>0.1887218045112782</v>
+        <v>0.0558974358974359</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>4.51</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.1002222222222222</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.4137614678899082</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>4.51</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.1002222222222222</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.4137614678899082</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>1.84</v>
+        <v>40.2</v>
       </c>
       <c r="V10">
-        <v>2.314465408805031</v>
+        <v>0.8933333333333334</v>
       </c>
       <c r="W10">
-        <v>0.06338383838383839</v>
+        <v>0.09749552772808587</v>
       </c>
       <c r="X10">
-        <v>0.1784126530671023</v>
+        <v>0.1673419957785876</v>
       </c>
       <c r="Y10">
-        <v>-0.1150288146832639</v>
+        <v>-0.06984646805050176</v>
       </c>
       <c r="Z10">
-        <v>0.6974305191400105</v>
+        <v>2.819007006605832</v>
       </c>
       <c r="AA10">
-        <v>0.09881527503056249</v>
+        <v>0.1367962851684956</v>
       </c>
       <c r="AB10">
-        <v>0.17185875175732</v>
+        <v>0.1663472750141894</v>
       </c>
       <c r="AC10">
-        <v>-0.07304347672675747</v>
+        <v>-0.02955098984569379</v>
       </c>
       <c r="AD10">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>0.7852938382391013</v>
       </c>
       <c r="AF10">
-        <v>0.077</v>
+        <v>0.7852938382391013</v>
       </c>
       <c r="AG10">
-        <v>-1.763</v>
+        <v>-39.4147061617609</v>
       </c>
       <c r="AH10">
-        <v>0.08830275229357798</v>
+        <v>0.01715166098995825</v>
       </c>
       <c r="AI10">
-        <v>0.02342561606327959</v>
+        <v>0.007730389001872416</v>
       </c>
       <c r="AJ10">
-        <v>1.821280991735537</v>
+        <v>-7.056872440964964</v>
       </c>
       <c r="AK10">
-        <v>-1.218382861091915</v>
+        <v>-0.6420871139857292</v>
       </c>
       <c r="AL10">
-        <v>0.006</v>
+        <v>0.063</v>
       </c>
       <c r="AM10">
-        <v>0.006</v>
+        <v>0.063</v>
       </c>
       <c r="AN10">
-        <v>0.2950191570881226</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>41.16666666666666</v>
+        <v>209.5238095238095</v>
       </c>
       <c r="AP10">
-        <v>-6.754789272030652</v>
+        <v>-2.726906473070493</v>
       </c>
       <c r="AQ10">
-        <v>41.16666666666666</v>
+        <v>209.5238095238095</v>
       </c>
     </row>
     <row r="11">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Crescent Star Insurance Limited (KASE:CSIL)</t>
+          <t>Askari General Insurance Company Limited (KASE:AGIC)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1785,109 +1785,121 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.161</v>
+        <v>0.107</v>
+      </c>
+      <c r="E11">
+        <v>0.0367</v>
       </c>
       <c r="G11">
-        <v>0.3914728682170542</v>
+        <v>0.2611650485436893</v>
       </c>
       <c r="H11">
-        <v>0.3914728682170542</v>
+        <v>0.2611650485436893</v>
       </c>
       <c r="I11">
-        <v>0.3811369509043928</v>
+        <v>0.2074686388266285</v>
       </c>
       <c r="J11">
-        <v>0.3266888150609081</v>
+        <v>0.1209891368998854</v>
       </c>
       <c r="K11">
-        <v>0.265</v>
+        <v>1.18</v>
       </c>
       <c r="L11">
-        <v>0.3423772609819122</v>
+        <v>0.1145631067961165</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>0.476</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.09577464788732394</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>0.4033898305084746</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>0.476</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.09577464788732394</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0.4033898305084746</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
       <c r="U11">
-        <v>0.014</v>
+        <v>1.43</v>
       </c>
       <c r="V11">
-        <v>0.01886792452830189</v>
+        <v>0.2877263581488934</v>
       </c>
       <c r="W11">
-        <v>0.05824175824175825</v>
+        <v>0.1145631067961165</v>
       </c>
       <c r="X11">
-        <v>0.1694296081871153</v>
+        <v>0.1802317579568904</v>
       </c>
       <c r="Y11">
-        <v>-0.1111878499453571</v>
+        <v>-0.06566865116077387</v>
       </c>
       <c r="Z11">
-        <v>0.177319587628866</v>
+        <v>1.028727967536767</v>
       </c>
       <c r="AA11">
-        <v>0.05792832596956308</v>
+        <v>0.1244649088970467</v>
       </c>
       <c r="AB11">
-        <v>0.1694296081871153</v>
+        <v>0.1712640289868466</v>
       </c>
       <c r="AC11">
-        <v>-0.1115012822175523</v>
+        <v>-0.04679912008979992</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>0.597</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>0.2003651004286306</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>0.7973651004286305</v>
       </c>
       <c r="AG11">
-        <v>-0.014</v>
+        <v>-0.6326348995713694</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>0.1382546598912856</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>0.08273683648170256</v>
       </c>
       <c r="AJ11">
-        <v>-0.01923076923076923</v>
+        <v>-0.1458569626773754</v>
       </c>
       <c r="AK11">
-        <v>-0.004004576659038902</v>
+        <v>-0.07708136433924817</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>0.2780624126688402</v>
+      </c>
+      <c r="AO11">
+        <v>24.70588235294118</v>
       </c>
       <c r="AP11">
-        <v>-0.04034582132564842</v>
+        <v>-0.2946599439084162</v>
+      </c>
+      <c r="AQ11">
+        <v>24.70588235294118</v>
       </c>
     </row>
     <row r="12">
@@ -1907,46 +1919,46 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.08119999999999999</v>
+        <v>0.193</v>
       </c>
       <c r="E12">
-        <v>-0.05429999999999999</v>
+        <v>-0.0114</v>
       </c>
       <c r="G12">
-        <v>0.1248148148148148</v>
+        <v>0.09426751592356687</v>
       </c>
       <c r="H12">
-        <v>0.1248148148148148</v>
+        <v>0.09426751592356687</v>
       </c>
       <c r="I12">
-        <v>0.07925925925925925</v>
+        <v>0.0695859872611465</v>
       </c>
       <c r="J12">
-        <v>0.05962403491104398</v>
+        <v>0.0530248128399133</v>
       </c>
       <c r="K12">
-        <v>0.498</v>
+        <v>0.365</v>
       </c>
       <c r="L12">
-        <v>0.09222222222222222</v>
+        <v>0.05812101910828025</v>
       </c>
       <c r="M12">
-        <v>0.326</v>
+        <v>0.267</v>
       </c>
       <c r="N12">
-        <v>0.09939024390243903</v>
+        <v>0.09020270270270271</v>
       </c>
       <c r="O12">
-        <v>0.6546184738955824</v>
+        <v>0.7315068493150686</v>
       </c>
       <c r="P12">
-        <v>0.326</v>
+        <v>0.267</v>
       </c>
       <c r="Q12">
-        <v>0.09939024390243903</v>
+        <v>0.09020270270270271</v>
       </c>
       <c r="R12">
-        <v>0.6546184738955824</v>
+        <v>0.7315068493150686</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1955,73 +1967,73 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>2.47</v>
+        <v>0.419</v>
       </c>
       <c r="V12">
-        <v>0.753048780487805</v>
+        <v>0.1415540540540541</v>
       </c>
       <c r="W12">
-        <v>0.06907073509015256</v>
+        <v>0.07101167315175097</v>
       </c>
       <c r="X12">
-        <v>0.1735579817190289</v>
+        <v>0.1822756331619521</v>
       </c>
       <c r="Y12">
-        <v>-0.1044872466288763</v>
+        <v>-0.1112639600102011</v>
       </c>
       <c r="Z12">
-        <v>0.6343984962406015</v>
+        <v>2.230113636363637</v>
       </c>
       <c r="AA12">
-        <v>0.03782539808736343</v>
+        <v>0.1182513581799203</v>
       </c>
       <c r="AB12">
-        <v>0.1703689456910383</v>
+        <v>0.1716271267424003</v>
       </c>
       <c r="AC12">
-        <v>-0.1325435476036749</v>
+        <v>-0.05337576856247998</v>
       </c>
       <c r="AD12">
-        <v>0.146</v>
+        <v>0.542</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.146</v>
+        <v>0.542</v>
       </c>
       <c r="AG12">
-        <v>-2.324</v>
+        <v>0.1230000000000001</v>
       </c>
       <c r="AH12">
-        <v>0.04261529480443666</v>
+        <v>0.1547687035979441</v>
       </c>
       <c r="AI12">
-        <v>0.02762012864169505</v>
+        <v>0.1170120898100173</v>
       </c>
       <c r="AJ12">
-        <v>-2.430962343096236</v>
+        <v>0.03989620499513463</v>
       </c>
       <c r="AK12">
-        <v>-0.8252840909090912</v>
+        <v>0.02919534773320675</v>
       </c>
       <c r="AL12">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="AM12">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="AN12">
-        <v>0.3333333333333333</v>
+        <v>1.217977528089888</v>
       </c>
       <c r="AO12">
-        <v>18.60869565217391</v>
+        <v>18.20833333333333</v>
       </c>
       <c r="AP12">
-        <v>-5.305936073059361</v>
+        <v>0.2764044943820226</v>
       </c>
       <c r="AQ12">
-        <v>18.60869565217391</v>
+        <v>18.20833333333333</v>
       </c>
     </row>
     <row r="13">
@@ -2032,7 +2044,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Reliance Insurance Company Limited (KASE:RICL)</t>
+          <t>Crescent Star Insurance Limited (KASE:CSIL)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2041,103 +2053,97 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.006500000000000001</v>
-      </c>
-      <c r="E13">
-        <v>0.0699</v>
+        <v>0.09029999999999999</v>
       </c>
       <c r="G13">
-        <v>0.2557471264367816</v>
+        <v>0.1705882352941176</v>
       </c>
       <c r="H13">
-        <v>0.2557471264367816</v>
+        <v>0.1705882352941176</v>
       </c>
       <c r="I13">
-        <v>0.1393277846988615</v>
+        <v>0.3480392156862745</v>
       </c>
       <c r="J13">
-        <v>0.09806762528160211</v>
+        <v>0.3480392156862745</v>
       </c>
       <c r="K13">
-        <v>0.163</v>
+        <v>0.334</v>
       </c>
       <c r="L13">
-        <v>0.09367816091954023</v>
+        <v>0.3274509803921569</v>
       </c>
       <c r="M13">
-        <v>0.127</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.0675531914893617</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>0.7791411042944785</v>
+        <v>-0</v>
       </c>
       <c r="P13">
-        <v>0.127</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.0675531914893617</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>0.7791411042944785</v>
+        <v>-0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>0.639</v>
+        <v>0.022</v>
       </c>
       <c r="V13">
-        <v>0.3398936170212766</v>
+        <v>0.02460850111856823</v>
       </c>
       <c r="W13">
-        <v>0.02667757774140753</v>
+        <v>0.09100817438692099</v>
       </c>
       <c r="X13">
-        <v>0.1698167911436287</v>
+        <v>0.1657688276676707</v>
       </c>
       <c r="Y13">
-        <v>-0.1431392134022211</v>
+        <v>-0.07476065328074968</v>
       </c>
       <c r="Z13">
-        <v>0.3419913304397774</v>
+        <v>0.2889518413597734</v>
       </c>
       <c r="AA13">
-        <v>0.03353827764312466</v>
+        <v>0.1005665722379603</v>
       </c>
       <c r="AB13">
-        <v>0.1695439712990963</v>
+        <v>0.1657688276676707</v>
       </c>
       <c r="AC13">
-        <v>-0.1360056936559716</v>
+        <v>-0.06520225542971035</v>
       </c>
       <c r="AD13">
         <v>0</v>
       </c>
       <c r="AE13">
-        <v>0.007848273119904572</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.007848273119904572</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>-0.6311517268800955</v>
+        <v>-0.022</v>
       </c>
       <c r="AH13">
-        <v>0.004157258415123755</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>0.001706944782364266</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>-0.505387035771236</v>
+        <v>-0.02522935779816514</v>
       </c>
       <c r="AK13">
-        <v>-0.1594281173051108</v>
+        <v>-0.007806955287437899</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2149,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>-2.125089989495271</v>
+        <v>-0.05759162303664921</v>
       </c>
     </row>
     <row r="14">
@@ -2160,7 +2166,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TPL Insurance Limited (KASE:TPLI)</t>
+          <t>Reliance Insurance Company Limited (KASE:RICL)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2169,115 +2175,115 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.141</v>
+        <v>0.0922</v>
+      </c>
+      <c r="E14">
+        <v>0.192</v>
       </c>
       <c r="G14">
-        <v>0.02698412698412699</v>
+        <v>0.1644230769230769</v>
       </c>
       <c r="H14">
-        <v>0.02698412698412699</v>
+        <v>0.1644230769230769</v>
       </c>
       <c r="I14">
-        <v>-0.005474532011518512</v>
+        <v>0.2714521523079204</v>
       </c>
       <c r="J14">
-        <v>-0.005474532011518512</v>
+        <v>0.1687150529969366</v>
       </c>
       <c r="K14">
-        <v>-0.358</v>
+        <v>0.358</v>
       </c>
       <c r="L14">
-        <v>-0.02841269841269841</v>
+        <v>0.1721153846153846</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>0.106</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.0462882096069869</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>0.2960893854748604</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>0.106</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.0462882096069869</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>0.2960893854748604</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
       <c r="U14">
-        <v>6.42</v>
+        <v>0.465</v>
       </c>
       <c r="V14">
-        <v>0.436734693877551</v>
+        <v>0.203056768558952</v>
       </c>
       <c r="W14">
-        <v>-0.03891304347826087</v>
+        <v>0.07799564270152505</v>
       </c>
       <c r="X14">
-        <v>0.1766846683620988</v>
+        <v>0.166040358398681</v>
       </c>
       <c r="Y14">
-        <v>-0.2155977118403596</v>
+        <v>-0.08804471569715595</v>
       </c>
       <c r="Z14">
-        <v>3.157977432536949</v>
+        <v>0.5255315325976959</v>
       </c>
       <c r="AA14">
-        <v>-0.01728844854607657</v>
+        <v>0.08866508037378158</v>
       </c>
       <c r="AB14">
-        <v>0.1716211176135785</v>
+        <v>0.1658824976441862</v>
       </c>
       <c r="AC14">
-        <v>-0.188909566159655</v>
+        <v>-0.07721741727040464</v>
       </c>
       <c r="AD14">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>0.04989551672566622</v>
+        <v>0.006897615997628127</v>
       </c>
       <c r="AF14">
-        <v>1.149895516725666</v>
+        <v>0.006897615997628127</v>
       </c>
       <c r="AG14">
-        <v>-5.270104483274333</v>
+        <v>-0.4581023840023719</v>
       </c>
       <c r="AH14">
-        <v>0.0725490912865788</v>
+        <v>0.003003014130707013</v>
       </c>
       <c r="AI14">
-        <v>0.1129574969444801</v>
+        <v>0.001774581344576465</v>
       </c>
       <c r="AJ14">
-        <v>-0.55887199109755</v>
+        <v>-0.2500698619845603</v>
       </c>
       <c r="AK14">
-        <v>-1.401662482329787</v>
+        <v>-0.1338737844933492</v>
       </c>
       <c r="AL14">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>-14.28571428571429</v>
-      </c>
-      <c r="AO14">
-        <v>-0.6862745098039216</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>68.44291536719913</v>
-      </c>
-      <c r="AQ14">
-        <v>-0.6862745098039216</v>
+        <v>-0.7522206633864892</v>
       </c>
     </row>
     <row r="15">
@@ -2288,7 +2294,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Universal Insurance Company Limited (KASE:UVIC)</t>
+          <t>The Pakistan General Insurance Company Limited (KASE:PKGI)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2297,25 +2303,25 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.114</v>
+        <v>-0.413</v>
       </c>
       <c r="G15">
-        <v>-0.6675126903553299</v>
+        <v>-5.5</v>
       </c>
       <c r="H15">
-        <v>-0.6675126903553299</v>
+        <v>-5.5</v>
       </c>
       <c r="I15">
-        <v>-0.9314720812182741</v>
+        <v>-4.55</v>
       </c>
       <c r="J15">
-        <v>-0.9314720812182741</v>
+        <v>-4.55</v>
       </c>
       <c r="K15">
-        <v>-0.099</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="L15">
-        <v>-0.2512690355329949</v>
+        <v>-4.3</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2339,31 +2345,31 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>0.183</v>
+        <v>0.001</v>
       </c>
       <c r="V15">
-        <v>0.1869254341164454</v>
+        <v>0.0009708737864077669</v>
       </c>
       <c r="W15">
-        <v>-0.02045454545454545</v>
+        <v>-0.04321608040201005</v>
       </c>
       <c r="X15">
-        <v>0.1694296081871153</v>
+        <v>0.1657688276676707</v>
       </c>
       <c r="Y15">
-        <v>-0.1898841536416608</v>
+        <v>-0.2089849080696807</v>
       </c>
       <c r="Z15">
-        <v>0.08191268191268192</v>
+        <v>0.01006036217303823</v>
       </c>
       <c r="AA15">
-        <v>-0.0762993762993763</v>
+        <v>-0.04577464788732395</v>
       </c>
       <c r="AB15">
-        <v>0.1694296081871153</v>
+        <v>0.1657688276676707</v>
       </c>
       <c r="AC15">
-        <v>-0.2457289844864916</v>
+        <v>-0.2115434755549946</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -2375,7 +2381,7 @@
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>-0.183</v>
+        <v>-0.001</v>
       </c>
       <c r="AH15">
         <v>0</v>
@@ -2384,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="AJ15">
-        <v>-0.2298994974874372</v>
+        <v>-0.0009718172983479104</v>
       </c>
       <c r="AK15">
-        <v>-0.05706267539756781</v>
+        <v>-0.00066711140760507</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2399,7 +2405,7 @@
         <v>-0</v>
       </c>
       <c r="AP15">
-        <v>0.5169491525423729</v>
+        <v>0.01492537313432836</v>
       </c>
     </row>
     <row r="16">
@@ -2410,7 +2416,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Pakistan General Insurance Company Limited (KASE:PKGI)</t>
+          <t>Premier Insurance Limited (KASE:PINL)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2419,112 +2425,118 @@
         </is>
       </c>
       <c r="D16">
-        <v>-0.54</v>
-      </c>
-      <c r="E16">
-        <v>-0.182</v>
+        <v>0.0175</v>
       </c>
       <c r="G16">
-        <v>-8.653846153846155</v>
+        <v>-0.9250000000000002</v>
       </c>
       <c r="H16">
-        <v>-8.653846153846155</v>
+        <v>-0.9250000000000002</v>
       </c>
       <c r="I16">
-        <v>-8.153846153846153</v>
+        <v>-0.3391666666666667</v>
       </c>
       <c r="J16">
-        <v>-8.153846153846153</v>
+        <v>-0.3391666666666667</v>
       </c>
       <c r="K16">
-        <v>0.08400000000000001</v>
+        <v>-0.269</v>
       </c>
       <c r="L16">
-        <v>3.230769230769231</v>
+        <v>-0.2241666666666667</v>
       </c>
       <c r="M16">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="N16">
-        <v>-0</v>
+        <v>0.0007142857142857144</v>
       </c>
       <c r="O16">
-        <v>-0</v>
+        <v>-0.003717472118959108</v>
       </c>
       <c r="P16">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="Q16">
-        <v>-0</v>
+        <v>0.0007142857142857144</v>
       </c>
       <c r="R16">
-        <v>-0</v>
+        <v>-0.003717472118959108</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
       <c r="U16">
-        <v>0.002</v>
+        <v>0.209</v>
       </c>
       <c r="V16">
-        <v>0.001515151515151515</v>
+        <v>0.1492857142857143</v>
       </c>
       <c r="W16">
-        <v>0.0347107438016529</v>
+        <v>-0.05964523281596453</v>
       </c>
       <c r="X16">
-        <v>0.1694296081871153</v>
+        <v>0.1667346976781426</v>
       </c>
       <c r="Y16">
-        <v>-0.1347188643854624</v>
+        <v>-0.2263799304941072</v>
       </c>
       <c r="Z16">
-        <v>0.01076604554865424</v>
+        <v>0.2800466744457409</v>
       </c>
       <c r="AA16">
-        <v>-0.08778467908902692</v>
+        <v>-0.09498249708284713</v>
       </c>
       <c r="AB16">
-        <v>0.1694296081871153</v>
+        <v>0.1662455308682178</v>
       </c>
       <c r="AC16">
-        <v>-0.2572142872761423</v>
+        <v>-0.2612280279510649</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="AG16">
-        <v>-0.002</v>
+        <v>-0.194</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>0.01060070671378092</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>0.005917159763313609</v>
       </c>
       <c r="AJ16">
-        <v>-0.001517450682852807</v>
+        <v>-0.1608623548922057</v>
       </c>
       <c r="AK16">
-        <v>-0.001006036217303823</v>
+        <v>-0.08340498710232158</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AN16">
-        <v>-0</v>
+        <v>-0.03807106598984771</v>
+      </c>
+      <c r="AO16">
+        <v>-135.6666666666667</v>
       </c>
       <c r="AP16">
-        <v>0.01136363636363636</v>
+        <v>0.4923857868020304</v>
+      </c>
+      <c r="AQ16">
+        <v>-135.6666666666667</v>
       </c>
     </row>
     <row r="17">
@@ -2535,7 +2547,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Premier Insurance Limited (KASE:PINL)</t>
+          <t>The Universal Insurance Company Limited (KASE:UVIC)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2544,25 +2556,25 @@
         </is>
       </c>
       <c r="D17">
-        <v>-0.179</v>
+        <v>0.428</v>
       </c>
       <c r="G17">
-        <v>-0.2801470588235294</v>
+        <v>-2.019230769230769</v>
       </c>
       <c r="H17">
-        <v>-0.2801470588235294</v>
+        <v>-2.019230769230769</v>
       </c>
       <c r="I17">
-        <v>-0.575</v>
+        <v>-1.256410256410256</v>
       </c>
       <c r="J17">
-        <v>-0.575</v>
+        <v>-1.256410256410256</v>
       </c>
       <c r="K17">
-        <v>-0.599</v>
+        <v>-0.178</v>
       </c>
       <c r="L17">
-        <v>-0.4404411764705882</v>
+        <v>-0.5705128205128205</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2586,73 +2598,67 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>0.262</v>
+        <v>0.052</v>
       </c>
       <c r="V17">
-        <v>0.1884892086330935</v>
+        <v>0.04227642276422764</v>
       </c>
       <c r="W17">
-        <v>-0.07729032258064515</v>
+        <v>-0.05250737463126843</v>
       </c>
       <c r="X17">
-        <v>0.1718984138037164</v>
+        <v>0.1657688276676707</v>
       </c>
       <c r="Y17">
-        <v>-0.2491887363843616</v>
+        <v>-0.2182762022989391</v>
       </c>
       <c r="Z17">
-        <v>0.1851095685313734</v>
+        <v>0.09728718428437791</v>
       </c>
       <c r="AA17">
-        <v>-0.1064380019055397</v>
+        <v>-0.1222326161521671</v>
       </c>
       <c r="AB17">
-        <v>0.1702128378319891</v>
+        <v>0.1657688276676707</v>
       </c>
       <c r="AC17">
-        <v>-0.2766508397375288</v>
+        <v>-0.2880014438198378</v>
       </c>
       <c r="AD17">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>-0.225</v>
+        <v>-0.052</v>
       </c>
       <c r="AH17">
-        <v>0.02592852137351086</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>0.008137233340664175</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>-0.1931330472103005</v>
+        <v>-0.04414261460101868</v>
       </c>
       <c r="AK17">
-        <v>-0.05250875145857643</v>
+        <v>-0.01871850251979841</v>
       </c>
       <c r="AL17">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>-0.05027173913043478</v>
-      </c>
-      <c r="AO17">
-        <v>-130.3333333333333</v>
+        <v>-0</v>
       </c>
       <c r="AP17">
-        <v>0.3057065217391304</v>
-      </c>
-      <c r="AQ17">
-        <v>-130.3333333333333</v>
+        <v>0.1372031662269129</v>
       </c>
     </row>
   </sheetData>
